--- a/2026-A-alumnos.xlsx
+++ b/2026-A-alumnos.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ronin/Develop/ADA-2026-A/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E640F4F8-1C54-624B-82C5-DD4EC2B52F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F57CF8E-10A2-BC40-A92D-AF08B2ED1468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2680" yWindow="3120" windowWidth="26600" windowHeight="19960" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6960" yWindow="8080" windowWidth="26740" windowHeight="19660" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Alumnos" sheetId="1" r:id="rId1"/>
     <sheet name="Tareas" sheetId="2" r:id="rId2"/>
     <sheet name="Evaluaciones" sheetId="3" r:id="rId3"/>
+    <sheet name="SMP" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="133">
-  <si>
-    <t>ADA 2026-A</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="158">
   <si>
     <t>No</t>
   </si>
@@ -340,9 +338,6 @@
     <t>Ciclo</t>
   </si>
   <si>
-    <t>2025-A</t>
-  </si>
-  <si>
     <t>SMP práctica</t>
   </si>
   <si>
@@ -438,6 +433,88 @@
   <si>
     <t>Asignación de tareas</t>
   </si>
+  <si>
+    <t>Requisitos</t>
+  </si>
+  <si>
+    <t>Datos</t>
+  </si>
+  <si>
+    <t>2026-A</t>
+  </si>
+  <si>
+    <t>ADA</t>
+  </si>
+  <si>
+    <t>Articulo IEEE
+word, PDF</t>
+  </si>
+  <si>
+    <t>Código</t>
+  </si>
+  <si>
+    <t>Carpeta SRC</t>
+  </si>
+  <si>
+    <t>Carpeta DAT</t>
+  </si>
+  <si>
+    <t>Arch aux</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Calif</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>Word / PDF</t>
+  </si>
+  <si>
+    <t>Juan Pablo Gonzalez Mendoza</t>
+  </si>
+  <si>
+    <t>Grafica NO realista</t>
+  </si>
+  <si>
+    <t>No concuerdan datos con grafica</t>
+  </si>
+  <si>
+    <t>Si pero</t>
+  </si>
+  <si>
+    <t>Comentarios</t>
+  </si>
+  <si>
+    <t>Resultados no analizados y conclusiones que no son, etc.</t>
+  </si>
+  <si>
+    <t>Problemas en general</t>
+  </si>
+  <si>
+    <t>Sin objetivos</t>
+  </si>
+  <si>
+    <t>Mal redactados</t>
+  </si>
+  <si>
+    <t>Sin bibliografia</t>
+  </si>
+  <si>
+    <t>No s e respeto la estructura</t>
+  </si>
+  <si>
+    <t>Mal creada o no citada</t>
+  </si>
+  <si>
+    <t>Analisis de resultados</t>
+  </si>
+  <si>
+    <t>Lectura de datos lineal, algoritmo cuadratico?</t>
+  </si>
 </sst>
 </file>
 
@@ -446,7 +523,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -554,8 +631,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -604,8 +687,26 @@
         <bgColor theme="0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor rgb="FF8DB3E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="41">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -1171,13 +1272,91 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF505050"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF505050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF505050"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF505050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF505050"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1520,12 +1699,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1568,7 +1741,7 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1585,6 +1758,120 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1818,25 +2105,25 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>0</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="F2" s="7"/>
     </row>
     <row r="3" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="7"/>
       <c r="C3" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F3" s="7"/>
     </row>
@@ -1846,19 +2133,19 @@
     </row>
     <row r="5" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D5" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="F5" s="43" t="s">
         <v>4</v>
-      </c>
-      <c r="F5" s="43" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1866,13 +2153,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="E6" s="40" t="s">
         <v>7</v>
-      </c>
-      <c r="E6" s="40" t="s">
-        <v>8</v>
       </c>
       <c r="F6" s="44"/>
     </row>
@@ -1881,13 +2168,13 @@
         <v>2</v>
       </c>
       <c r="C7" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="E7" s="39" t="s">
         <v>10</v>
-      </c>
-      <c r="E7" s="39" t="s">
-        <v>11</v>
       </c>
       <c r="F7" s="45"/>
     </row>
@@ -1896,13 +2183,13 @@
         <v>3</v>
       </c>
       <c r="C8" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>13</v>
-      </c>
       <c r="E8" s="40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" s="44"/>
     </row>
@@ -1911,13 +2198,13 @@
         <v>4</v>
       </c>
       <c r="C9" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="15" t="s">
-        <v>15</v>
-      </c>
       <c r="E9" s="39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" s="45"/>
     </row>
@@ -1926,13 +2213,13 @@
         <v>5</v>
       </c>
       <c r="C10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="E10" s="40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" s="44"/>
     </row>
@@ -1941,13 +2228,13 @@
         <v>6</v>
       </c>
       <c r="C11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="115" t="s">
-        <v>19</v>
-      </c>
       <c r="E11" s="39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" s="45"/>
     </row>
@@ -1956,13 +2243,13 @@
         <v>7</v>
       </c>
       <c r="C12" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>21</v>
-      </c>
       <c r="E12" s="40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" s="44"/>
     </row>
@@ -1971,13 +2258,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="15" t="s">
-        <v>23</v>
-      </c>
       <c r="E13" s="39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F13" s="45"/>
     </row>
@@ -1986,13 +2273,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>25</v>
-      </c>
       <c r="E14" s="40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" s="44"/>
     </row>
@@ -2001,13 +2288,13 @@
         <v>10</v>
       </c>
       <c r="C15" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="46" t="s">
-        <v>27</v>
-      </c>
       <c r="E15" s="39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" s="45"/>
     </row>
@@ -2016,13 +2303,13 @@
         <v>11</v>
       </c>
       <c r="C16" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>29</v>
-      </c>
       <c r="E16" s="40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F16" s="44"/>
     </row>
@@ -2031,13 +2318,13 @@
         <v>12</v>
       </c>
       <c r="C17" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="46" t="s">
-        <v>31</v>
-      </c>
       <c r="E17" s="39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F17" s="45"/>
     </row>
@@ -2046,13 +2333,13 @@
         <v>13</v>
       </c>
       <c r="C18" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="E18" s="40" t="s">
         <v>33</v>
-      </c>
-      <c r="E18" s="40" t="s">
-        <v>34</v>
       </c>
       <c r="F18" s="44"/>
     </row>
@@ -2061,13 +2348,13 @@
         <v>14</v>
       </c>
       <c r="C19" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="47" t="s">
-        <v>36</v>
-      </c>
       <c r="E19" s="41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F19" s="48"/>
     </row>
@@ -6020,7 +6307,7 @@
     <col min="3" max="3" width="31.33203125" customWidth="1"/>
     <col min="4" max="4" width="20.33203125" customWidth="1"/>
     <col min="5" max="5" width="34.5" customWidth="1"/>
-    <col min="6" max="6" width="19.83203125" style="136" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" style="134" customWidth="1"/>
     <col min="7" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6030,7 +6317,7 @@
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
       <c r="E1" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="1"/>
@@ -6057,8 +6344,8 @@
     <row r="2" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="137" t="s">
-        <v>132</v>
+      <c r="C2" s="135" t="s">
+        <v>130</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="1"/>
@@ -6114,20 +6401,20 @@
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
-      <c r="B4" s="122" t="s">
+      <c r="B4" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="123" t="s">
-        <v>2</v>
+      <c r="D4" s="121" t="s">
+        <v>36</v>
       </c>
-      <c r="D4" s="123" t="s">
+      <c r="E4" s="121" t="s">
+        <v>129</v>
+      </c>
+      <c r="F4" s="122" t="s">
         <v>37</v>
-      </c>
-      <c r="E4" s="123" t="s">
-        <v>131</v>
-      </c>
-      <c r="F4" s="124" t="s">
-        <v>38</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -6152,21 +6439,21 @@
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
-      <c r="B5" s="125">
+      <c r="B5" s="123">
         <v>1</v>
       </c>
-      <c r="C5" s="119" t="str">
+      <c r="C5" s="117" t="str">
         <f>Alumnos!C6</f>
         <v>Ceballos Conde Emanuel</v>
       </c>
-      <c r="D5" s="118" t="s">
+      <c r="D5" s="116" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="118" t="s">
+      <c r="F5" s="131" t="s">
         <v>40</v>
-      </c>
-      <c r="F5" s="133" t="s">
-        <v>41</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -6191,21 +6478,21 @@
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="126">
+      <c r="B6" s="124">
         <v>2</v>
       </c>
-      <c r="C6" s="121" t="str">
+      <c r="C6" s="119" t="str">
         <f>Alumnos!C7</f>
         <v>Conde Angeles Eduardo</v>
       </c>
-      <c r="D6" s="120" t="s">
+      <c r="D6" s="118" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="118" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="120" t="s">
+      <c r="F6" s="131" t="s">
         <v>43</v>
-      </c>
-      <c r="F6" s="133" t="s">
-        <v>44</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -6230,21 +6517,21 @@
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="B7" s="125">
+      <c r="B7" s="123">
         <v>3</v>
       </c>
-      <c r="C7" s="119" t="str">
+      <c r="C7" s="117" t="str">
         <f>Alumnos!C8</f>
         <v>González Lugo Arlet Linette</v>
       </c>
-      <c r="D7" s="118" t="s">
+      <c r="D7" s="116" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="118" t="s">
+      <c r="F7" s="131" t="s">
         <v>46</v>
-      </c>
-      <c r="F7" s="133" t="s">
-        <v>47</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -6269,21 +6556,21 @@
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="126">
+      <c r="B8" s="124">
         <v>4</v>
       </c>
-      <c r="C8" s="121" t="str">
+      <c r="C8" s="119" t="str">
         <f>Alumnos!C9</f>
         <v>Guerra Ortiz Guadalupe</v>
       </c>
-      <c r="D8" s="120" t="s">
+      <c r="D8" s="118" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="120" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="134" t="s">
-        <v>41</v>
+      <c r="F8" s="132" t="s">
+        <v>40</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -6308,21 +6595,21 @@
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="125">
+      <c r="B9" s="123">
         <v>5</v>
       </c>
-      <c r="C9" s="119" t="str">
+      <c r="C9" s="117" t="str">
         <f>Alumnos!C10</f>
         <v>Hernández González Alan Yair</v>
       </c>
-      <c r="D9" s="118" t="s">
+      <c r="D9" s="116" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="116" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="134" t="s">
-        <v>44</v>
+      <c r="F9" s="132" t="s">
+        <v>43</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -6347,21 +6634,21 @@
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="126">
+      <c r="B10" s="124">
         <v>6</v>
       </c>
-      <c r="C10" s="121" t="str">
+      <c r="C10" s="119" t="str">
         <f>Alumnos!C11</f>
         <v>Jara Neira Jalton Efrain</v>
       </c>
-      <c r="D10" s="120" t="s">
+      <c r="D10" s="118" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="120" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="134" t="s">
-        <v>47</v>
+      <c r="F10" s="132" t="s">
+        <v>46</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -6386,21 +6673,21 @@
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="125">
+      <c r="B11" s="123">
         <v>7</v>
       </c>
-      <c r="C11" s="119" t="str">
+      <c r="C11" s="117" t="str">
         <f>Alumnos!C12</f>
         <v>Jiménez Venegas Sofia</v>
       </c>
-      <c r="D11" s="118" t="s">
+      <c r="D11" s="116" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="116" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="118" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="133" t="s">
-        <v>41</v>
+      <c r="F11" s="131" t="s">
+        <v>40</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -6425,21 +6712,21 @@
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
-      <c r="B12" s="126">
+      <c r="B12" s="124">
         <v>8</v>
       </c>
-      <c r="C12" s="121" t="str">
+      <c r="C12" s="119" t="str">
         <f>Alumnos!C13</f>
         <v>Mendoza Hernández Beatriz</v>
       </c>
-      <c r="D12" s="130" t="s">
-        <v>39</v>
+      <c r="D12" s="128" t="s">
+        <v>38</v>
       </c>
-      <c r="E12" s="120" t="s">
-        <v>56</v>
+      <c r="E12" s="118" t="s">
+        <v>55</v>
       </c>
-      <c r="F12" s="133" t="s">
-        <v>44</v>
+      <c r="F12" s="131" t="s">
+        <v>43</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -6464,21 +6751,21 @@
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="125">
+      <c r="B13" s="123">
         <v>9</v>
       </c>
-      <c r="C13" s="119" t="str">
+      <c r="C13" s="117" t="str">
         <f>Alumnos!C14</f>
         <v>Pablo Aparicio Metztli Donaji</v>
       </c>
-      <c r="D13" s="132" t="s">
-        <v>42</v>
+      <c r="D13" s="130" t="s">
+        <v>41</v>
       </c>
-      <c r="E13" s="118" t="s">
-        <v>57</v>
+      <c r="E13" s="116" t="s">
+        <v>56</v>
       </c>
-      <c r="F13" s="133" t="s">
-        <v>47</v>
+      <c r="F13" s="131" t="s">
+        <v>46</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -6503,21 +6790,21 @@
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="126">
+      <c r="B14" s="124">
         <v>10</v>
       </c>
-      <c r="C14" s="121" t="str">
+      <c r="C14" s="119" t="str">
         <f>Alumnos!C15</f>
         <v>Ruiz Ramirez Juan Pablo</v>
       </c>
-      <c r="D14" s="130" t="s">
-        <v>45</v>
+      <c r="D14" s="128" t="s">
+        <v>44</v>
       </c>
-      <c r="E14" s="120" t="s">
-        <v>58</v>
+      <c r="E14" s="118" t="s">
+        <v>57</v>
       </c>
-      <c r="F14" s="134" t="s">
-        <v>41</v>
+      <c r="F14" s="132" t="s">
+        <v>40</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -6542,21 +6829,21 @@
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="125">
+      <c r="B15" s="123">
         <v>11</v>
       </c>
-      <c r="C15" s="119" t="str">
+      <c r="C15" s="117" t="str">
         <f>Alumnos!C16</f>
         <v>Torres Santiago Guillermo</v>
       </c>
-      <c r="D15" s="132" t="s">
-        <v>48</v>
+      <c r="D15" s="130" t="s">
+        <v>47</v>
       </c>
-      <c r="E15" s="118" t="s">
-        <v>59</v>
+      <c r="E15" s="116" t="s">
+        <v>58</v>
       </c>
-      <c r="F15" s="134" t="s">
-        <v>44</v>
+      <c r="F15" s="132" t="s">
+        <v>43</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -6581,21 +6868,21 @@
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
-      <c r="B16" s="126">
+      <c r="B16" s="124">
         <v>12</v>
       </c>
-      <c r="C16" s="121" t="str">
+      <c r="C16" s="119" t="str">
         <f>Alumnos!C17</f>
         <v>Vazquez de la Rosa Alejandro Neftali</v>
       </c>
-      <c r="D16" s="130" t="s">
-        <v>50</v>
+      <c r="D16" s="128" t="s">
+        <v>49</v>
       </c>
-      <c r="E16" s="120" t="s">
-        <v>60</v>
+      <c r="E16" s="118" t="s">
+        <v>59</v>
       </c>
-      <c r="F16" s="134" t="s">
-        <v>47</v>
+      <c r="F16" s="132" t="s">
+        <v>46</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -6620,21 +6907,21 @@
     </row>
     <row r="17" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
-      <c r="B17" s="125">
+      <c r="B17" s="123">
         <v>13</v>
       </c>
-      <c r="C17" s="119" t="str">
+      <c r="C17" s="117" t="str">
         <f>Alumnos!C18</f>
         <v>Braulio Alberto Ronquillo Núñez</v>
       </c>
-      <c r="D17" s="132" t="s">
-        <v>52</v>
+      <c r="D17" s="130" t="s">
+        <v>51</v>
       </c>
-      <c r="E17" s="118" t="s">
-        <v>61</v>
+      <c r="E17" s="116" t="s">
+        <v>60</v>
       </c>
-      <c r="F17" s="133" t="s">
-        <v>41</v>
+      <c r="F17" s="131" t="s">
+        <v>40</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -6659,21 +6946,21 @@
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="127">
+      <c r="B18" s="125">
         <v>14</v>
       </c>
-      <c r="C18" s="128" t="str">
+      <c r="C18" s="126" t="str">
         <f>Alumnos!C19</f>
         <v>Juan pablo Gonzalez mendoza</v>
       </c>
-      <c r="D18" s="131" t="s">
-        <v>54</v>
+      <c r="D18" s="129" t="s">
+        <v>53</v>
       </c>
-      <c r="E18" s="129" t="s">
-        <v>62</v>
+      <c r="E18" s="127" t="s">
+        <v>61</v>
       </c>
-      <c r="F18" s="135" t="s">
-        <v>44</v>
+      <c r="F18" s="133" t="s">
+        <v>43</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -6786,13 +7073,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="1"/>
@@ -6822,13 +7109,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="1"/>
@@ -34239,7 +34526,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="73" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B1" s="111">
         <v>0.8</v>
@@ -34278,73 +34565,73 @@
     </row>
     <row r="2" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="73" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B2" s="111">
         <v>0.2</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E2" s="74" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F2" s="114">
         <f>F3*$B$1/$C$1</f>
-        <v>3.6363636363636369E-2</v>
+        <v>7.2727272727272738E-2</v>
       </c>
       <c r="G2" s="114">
         <f t="shared" ref="G2:S2" si="0">G3*$B$1/$C$1</f>
-        <v>3.6363636363636369E-2</v>
+        <v>7.2727272727272738E-2</v>
       </c>
       <c r="H2" s="114">
         <f t="shared" si="0"/>
-        <v>3.6363636363636369E-2</v>
+        <v>7.2727272727272738E-2</v>
       </c>
       <c r="I2" s="114">
         <f t="shared" si="0"/>
-        <v>3.6363636363636369E-2</v>
+        <v>7.2727272727272738E-2</v>
       </c>
       <c r="J2" s="114">
         <f t="shared" si="0"/>
-        <v>3.6363636363636369E-2</v>
+        <v>7.2727272727272738E-2</v>
       </c>
       <c r="K2" s="114">
         <f t="shared" si="0"/>
-        <v>3.6363636363636369E-2</v>
+        <v>7.2727272727272738E-2</v>
       </c>
       <c r="L2" s="114">
         <f t="shared" si="0"/>
-        <v>3.6363636363636369E-2</v>
+        <v>7.2727272727272738E-2</v>
       </c>
       <c r="M2" s="114">
         <f t="shared" si="0"/>
-        <v>3.6363636363636369E-2</v>
+        <v>7.2727272727272738E-2</v>
       </c>
       <c r="N2" s="114">
         <f t="shared" si="0"/>
-        <v>3.6363636363636369E-2</v>
+        <v>7.2727272727272738E-2</v>
       </c>
       <c r="O2" s="114">
         <f t="shared" si="0"/>
-        <v>3.6363636363636369E-2</v>
+        <v>7.2727272727272738E-2</v>
       </c>
       <c r="P2" s="114">
         <f t="shared" si="0"/>
-        <v>3.6363636363636369E-2</v>
+        <v>7.2727272727272738E-2</v>
       </c>
       <c r="Q2" s="114">
         <f t="shared" si="0"/>
-        <v>3.6363636363636369E-2</v>
+        <v>7.2727272727272738E-2</v>
       </c>
       <c r="R2" s="114">
         <f t="shared" si="0"/>
-        <v>3.6363636363636369E-2</v>
+        <v>7.2727272727272738E-2</v>
       </c>
       <c r="S2" s="114">
         <f t="shared" si="0"/>
-        <v>3.6363636363636369E-2</v>
+        <v>7.2727272727272738E-2</v>
       </c>
       <c r="T2" s="73"/>
       <c r="U2" s="6"/>
@@ -34358,7 +34645,7 @@
     </row>
     <row r="3" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="73" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B3" s="111">
         <v>0.1</v>
@@ -34366,63 +34653,63 @@
       <c r="C3" s="7"/>
       <c r="D3" s="18"/>
       <c r="E3" s="74" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F3" s="74">
         <f>COUNTIF(F6:F40, "&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="74">
         <f t="shared" ref="G3:S3" si="1">COUNTIF(G6:G40, "&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="74">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="74">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="74">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="74">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="74">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="74">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" s="74">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" s="74">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3" s="74">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="74">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" s="74">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" s="74">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" s="73"/>
       <c r="U3" s="6"/>
@@ -34436,7 +34723,7 @@
     </row>
     <row r="4" spans="1:28" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="112" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" s="111">
         <f>SUM(B1:B3)</f>
@@ -34445,25 +34732,25 @@
       <c r="C4" s="7"/>
       <c r="D4" s="6"/>
       <c r="E4" s="72" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
-      <c r="F4" s="116" t="s">
-        <v>71</v>
+      <c r="F4" s="136" t="s">
+        <v>70</v>
       </c>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116"/>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116"/>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
+      <c r="K4" s="136"/>
+      <c r="L4" s="136"/>
+      <c r="M4" s="136"/>
+      <c r="N4" s="136"/>
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="136"/>
+      <c r="R4" s="136"/>
+      <c r="S4" s="136"/>
+      <c r="T4" s="136"/>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
       <c r="W4" s="6"/>
@@ -34477,10 +34764,10 @@
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
       <c r="C5" s="23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="71">
@@ -34543,29 +34830,29 @@
         <v>1</v>
       </c>
       <c r="C6" s="76" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E6" s="63">
         <f>COUNTIF(F6:T6, "&lt;&gt;")</f>
         <v>15</v>
       </c>
       <c r="F6" s="49" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G6" s="49" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H6" s="49" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I6" s="49" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J6" s="49" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K6" s="49">
         <v>1</v>
@@ -34613,26 +34900,54 @@
       </c>
       <c r="C7" s="28"/>
       <c r="D7" s="29" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E7" s="64">
         <f t="shared" ref="E7:E40" si="2">COUNTIF(F7:T7, "&lt;&gt;")</f>
+        <v>14</v>
+      </c>
+      <c r="F7" s="51">
+        <v>10</v>
+      </c>
+      <c r="G7" s="51">
+        <v>10</v>
+      </c>
+      <c r="H7" s="51">
+        <v>8</v>
+      </c>
+      <c r="I7" s="51">
+        <v>8</v>
+      </c>
+      <c r="J7" s="51">
+        <v>10</v>
+      </c>
+      <c r="K7" s="51">
+        <v>8</v>
+      </c>
+      <c r="L7" s="51">
+        <v>8</v>
+      </c>
+      <c r="M7" s="51">
+        <v>8</v>
+      </c>
+      <c r="N7" s="51">
+        <v>6</v>
+      </c>
+      <c r="O7" s="51">
+        <v>10</v>
+      </c>
+      <c r="P7" s="51">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="51">
+        <v>8</v>
+      </c>
+      <c r="R7" s="51">
+        <v>8</v>
+      </c>
+      <c r="S7" s="51">
         <v>0</v>
       </c>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="51"/>
       <c r="T7" s="52"/>
       <c r="U7" s="6"/>
       <c r="V7" s="6"/>
@@ -34649,10 +34964,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E8" s="63">
         <f t="shared" si="2"/>
@@ -34684,14 +34999,14 @@
     </row>
     <row r="9" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="6"/>
-      <c r="B9" s="117">
+      <c r="B9" s="137">
         <v>4</v>
       </c>
       <c r="C9" s="77" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E9" s="65">
         <f t="shared" si="2"/>
@@ -34723,10 +35038,10 @@
     </row>
     <row r="10" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="6"/>
-      <c r="B10" s="117"/>
+      <c r="B10" s="137"/>
       <c r="C10" s="33"/>
       <c r="D10" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E10" s="66">
         <f t="shared" si="2"/>
@@ -34758,10 +35073,10 @@
     </row>
     <row r="11" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="6"/>
-      <c r="B11" s="117"/>
+      <c r="B11" s="137"/>
       <c r="C11" s="32"/>
       <c r="D11" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E11" s="65">
         <f t="shared" si="2"/>
@@ -34798,7 +35113,7 @@
       </c>
       <c r="C12" s="34"/>
       <c r="D12" s="35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E12" s="67">
         <f t="shared" si="2"/>
@@ -34834,10 +35149,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="75" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E13" s="68">
         <f t="shared" si="2"/>
@@ -34873,10 +35188,10 @@
         <v>7</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E14" s="66">
         <f t="shared" si="2"/>
@@ -34913,7 +35228,7 @@
       </c>
       <c r="C15" s="32"/>
       <c r="D15" s="21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E15" s="65">
         <f t="shared" si="2"/>
@@ -34948,7 +35263,7 @@
       <c r="B16" s="7"/>
       <c r="C16" s="34"/>
       <c r="D16" s="35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E16" s="67">
         <f t="shared" si="2"/>
@@ -34984,10 +35299,10 @@
         <v>9</v>
       </c>
       <c r="C17" s="75" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E17" s="68">
         <f t="shared" si="2"/>
@@ -35023,10 +35338,10 @@
         <v>10</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E18" s="66">
         <f t="shared" si="2"/>
@@ -35063,7 +35378,7 @@
       </c>
       <c r="C19" s="32"/>
       <c r="D19" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19" s="65">
         <f t="shared" si="2"/>
@@ -35098,7 +35413,7 @@
       <c r="B20" s="7"/>
       <c r="C20" s="34"/>
       <c r="D20" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E20" s="67">
         <f t="shared" si="2"/>
@@ -35134,10 +35449,10 @@
         <v>12</v>
       </c>
       <c r="C21" s="75" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E21" s="68">
         <f t="shared" ref="E21:E24" si="3">COUNTIF(F21:T21, "&lt;&gt;")</f>
@@ -35173,10 +35488,10 @@
         <v>13</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E22" s="66">
         <f t="shared" si="3"/>
@@ -35213,7 +35528,7 @@
       </c>
       <c r="C23" s="32"/>
       <c r="D23" s="21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E23" s="65">
         <f t="shared" si="3"/>
@@ -35248,7 +35563,7 @@
       <c r="B24" s="7"/>
       <c r="C24" s="34"/>
       <c r="D24" s="35" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E24" s="67">
         <f t="shared" si="3"/>
@@ -35283,7 +35598,7 @@
       <c r="B25" s="7"/>
       <c r="C25" s="88"/>
       <c r="D25" s="37" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E25" s="89"/>
       <c r="F25" s="90"/>
@@ -35316,10 +35631,10 @@
         <v>15</v>
       </c>
       <c r="C26" s="75" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D26" s="36" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E26" s="68">
         <f t="shared" ref="E26:E29" si="4">COUNTIF(F26:T26, "&lt;&gt;")</f>
@@ -35356,7 +35671,7 @@
       </c>
       <c r="C27" s="33"/>
       <c r="D27" s="20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E27" s="66">
         <f t="shared" si="4"/>
@@ -35393,7 +35708,7 @@
       </c>
       <c r="C28" s="32"/>
       <c r="D28" s="21" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E28" s="65">
         <f t="shared" si="4"/>
@@ -35462,10 +35777,10 @@
         <v>18</v>
       </c>
       <c r="C30" s="75" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D30" s="36" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E30" s="68">
         <f t="shared" si="2"/>
@@ -35502,7 +35817,7 @@
       </c>
       <c r="C31" s="80"/>
       <c r="D31" s="20" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E31" s="66">
         <f t="shared" si="2"/>
@@ -35539,7 +35854,7 @@
       </c>
       <c r="C32" s="81"/>
       <c r="D32" s="31" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E32" s="69">
         <f t="shared" ref="E32:E35" si="5">COUNTIF(F32:T32, "&lt;&gt;")</f>
@@ -35574,7 +35889,7 @@
       <c r="B33" s="7"/>
       <c r="C33" s="80"/>
       <c r="D33" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E33" s="66">
         <f t="shared" si="5"/>
@@ -35609,7 +35924,7 @@
       <c r="B34" s="7"/>
       <c r="C34" s="81"/>
       <c r="D34" s="31" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E34" s="69">
         <f t="shared" si="5"/>
@@ -35644,7 +35959,7 @@
       <c r="B35" s="7"/>
       <c r="C35" s="80"/>
       <c r="D35" s="20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E35" s="66">
         <f t="shared" si="5"/>
@@ -35679,7 +35994,7 @@
       <c r="B36" s="7"/>
       <c r="C36" s="81"/>
       <c r="D36" s="31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E36" s="69">
         <f t="shared" ref="E36:E37" si="6">COUNTIF(F36:T36, "&lt;&gt;")</f>
@@ -35714,7 +36029,7 @@
       <c r="B37" s="7"/>
       <c r="C37" s="80"/>
       <c r="D37" s="20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E37" s="66">
         <f t="shared" si="6"/>
@@ -35749,7 +36064,7 @@
       <c r="B38" s="7"/>
       <c r="C38" s="83"/>
       <c r="D38" s="84" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E38" s="85">
         <f t="shared" ref="E38:E39" si="7">COUNTIF(F38:T38, "&lt;&gt;")</f>
@@ -35785,7 +36100,7 @@
         <v>21</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D39" s="26"/>
       <c r="E39" s="78">
@@ -35857,7 +36172,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="72" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F41" s="7">
         <f>COUNTIF(F43:F47, "&lt;&gt;")</f>
@@ -35933,7 +36248,7 @@
       <c r="B42" s="7"/>
       <c r="C42" s="23"/>
       <c r="D42" s="24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E42" s="24"/>
       <c r="F42" s="25">
@@ -36171,7 +36486,7 @@
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="72" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F48" s="7">
         <f>COUNTIF(F50:F54, "&lt;&gt;")</f>
@@ -36247,7 +36562,7 @@
       <c r="B49" s="7"/>
       <c r="C49" s="23"/>
       <c r="D49" s="24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E49" s="24"/>
       <c r="F49" s="25">
@@ -36311,7 +36626,7 @@
       </c>
       <c r="C50" s="98"/>
       <c r="D50" s="99" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E50" s="100">
         <f t="shared" ref="E50:E53" si="11">COUNTIF(F50:T50, "&lt;&gt;")</f>
@@ -65739,4 +66054,4510 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2EE4DD5-76DA-4242-9C34-A82D133C89CC}">
+  <dimension ref="B1:K1002"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.6640625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="33" style="6" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.5" style="6" customWidth="1"/>
+    <col min="6" max="6" width="9.83203125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="6" customWidth="1"/>
+    <col min="9" max="9" width="9.1640625" style="6" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" style="6" customWidth="1"/>
+    <col min="11" max="11" width="47.1640625" style="6" customWidth="1"/>
+    <col min="12" max="29" width="8.6640625" style="6" customWidth="1"/>
+    <col min="30" max="16384" width="14.5" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I2" s="7"/>
+    </row>
+    <row r="3" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="7"/>
+      <c r="C3" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="7"/>
+    </row>
+    <row r="4" spans="2:11" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="7"/>
+      <c r="D4" s="138" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" s="138"/>
+      <c r="F4" s="138"/>
+      <c r="G4" s="138"/>
+      <c r="H4" s="138"/>
+      <c r="I4" s="138"/>
+    </row>
+    <row r="5" spans="2:11" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="7"/>
+      <c r="D5" s="140"/>
+      <c r="E5" s="140"/>
+      <c r="F5" s="140" t="s">
+        <v>138</v>
+      </c>
+      <c r="G5" s="140" t="s">
+        <v>137</v>
+      </c>
+      <c r="H5" s="140"/>
+      <c r="I5" s="140"/>
+    </row>
+    <row r="6" spans="2:11" ht="29" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="139" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="141" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="152" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="153" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="154" t="s">
+        <v>132</v>
+      </c>
+      <c r="G6" s="154" t="s">
+        <v>136</v>
+      </c>
+      <c r="H6" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="I6" s="155" t="s">
+        <v>140</v>
+      </c>
+      <c r="J6" s="156" t="s">
+        <v>141</v>
+      </c>
+      <c r="K6" s="42" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="12">
+        <v>1</v>
+      </c>
+      <c r="C7" s="142" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="157" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" s="158" t="s">
+        <v>142</v>
+      </c>
+      <c r="F7" s="158" t="s">
+        <v>142</v>
+      </c>
+      <c r="G7" s="158" t="s">
+        <v>142</v>
+      </c>
+      <c r="H7" s="158" t="s">
+        <v>142</v>
+      </c>
+      <c r="I7" s="158">
+        <f>COUNTIF(D7:H7, "Si")</f>
+        <v>5</v>
+      </c>
+      <c r="J7" s="159">
+        <f>I7*10/5</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="14">
+        <v>2</v>
+      </c>
+      <c r="C8" s="143" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="149" t="s">
+        <v>142</v>
+      </c>
+      <c r="E8" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="F8" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="G8" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="H8" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="I8" s="146">
+        <f t="shared" ref="I8:I20" si="0">COUNTIF(D8:H8, "Si")</f>
+        <v>5</v>
+      </c>
+      <c r="J8" s="151">
+        <f t="shared" ref="J8:J20" si="1">I8*10/5</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="12">
+        <v>3</v>
+      </c>
+      <c r="C9" s="142" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="147" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="H9" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="I9" s="145">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J9" s="148">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="14">
+        <v>4</v>
+      </c>
+      <c r="C10" s="143" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="165" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" s="166" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" s="166" t="s">
+        <v>142</v>
+      </c>
+      <c r="G10" s="166" t="s">
+        <v>142</v>
+      </c>
+      <c r="H10" s="167" t="s">
+        <v>0</v>
+      </c>
+      <c r="I10" s="146">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J10" s="151">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="12">
+        <v>5</v>
+      </c>
+      <c r="C11" s="142" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="147" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="F11" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="G11" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="H11" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="I11" s="145">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J11" s="148">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="14">
+        <v>6</v>
+      </c>
+      <c r="C12" s="143" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="169" t="s">
+        <v>147</v>
+      </c>
+      <c r="E12" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="F12" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="G12" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="H12" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="I12" s="146">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J12" s="151">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="12">
+        <v>7</v>
+      </c>
+      <c r="C13" s="142" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="170" t="s">
+        <v>147</v>
+      </c>
+      <c r="E13" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="F13" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="G13" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="H13" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="I13" s="145">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J13" s="148">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="14">
+        <v>8</v>
+      </c>
+      <c r="C14" s="143" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="149" t="s">
+        <v>142</v>
+      </c>
+      <c r="E14" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="F14" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="G14" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="H14" s="161" t="s">
+        <v>147</v>
+      </c>
+      <c r="I14" s="146">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J14" s="151">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="12">
+        <v>9</v>
+      </c>
+      <c r="C15" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="170" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="F15" s="162" t="s">
+        <v>0</v>
+      </c>
+      <c r="G15" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="H15" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="I15" s="145">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J15" s="148">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="14">
+        <v>10</v>
+      </c>
+      <c r="C16" s="143" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="149" t="s">
+        <v>142</v>
+      </c>
+      <c r="E16" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="F16" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="G16" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="H16" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="I16" s="146">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J16" s="151">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="12">
+        <v>11</v>
+      </c>
+      <c r="C17" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="172" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17" s="173" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="173" t="s">
+        <v>142</v>
+      </c>
+      <c r="G17" s="173" t="s">
+        <v>142</v>
+      </c>
+      <c r="H17" s="173" t="s">
+        <v>142</v>
+      </c>
+      <c r="I17" s="145">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J17" s="148">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="14">
+        <v>12</v>
+      </c>
+      <c r="C18" s="143" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="149" t="s">
+        <v>142</v>
+      </c>
+      <c r="E18" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="F18" s="161" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="H18" s="146" t="s">
+        <v>142</v>
+      </c>
+      <c r="I18" s="146">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J18" s="151">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="12">
+        <v>13</v>
+      </c>
+      <c r="C19" s="142" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="170" t="s">
+        <v>0</v>
+      </c>
+      <c r="E19" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="G19" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="H19" s="145" t="s">
+        <v>142</v>
+      </c>
+      <c r="I19" s="145">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J19" s="148">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="16">
+        <v>14</v>
+      </c>
+      <c r="C20" s="144" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" s="163" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="164" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" s="164" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="164" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="164" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="160">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="7"/>
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="7"/>
+      <c r="C22" s="168" t="s">
+        <v>150</v>
+      </c>
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="7"/>
+      <c r="C23" s="73" t="s">
+        <v>151</v>
+      </c>
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="7"/>
+      <c r="C24" s="171" t="s">
+        <v>152</v>
+      </c>
+      <c r="I24" s="7"/>
+    </row>
+    <row r="25" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="7"/>
+      <c r="C25" s="73" t="s">
+        <v>153</v>
+      </c>
+      <c r="I25" s="7"/>
+    </row>
+    <row r="26" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="7"/>
+      <c r="C26" s="171" t="s">
+        <v>155</v>
+      </c>
+      <c r="I26" s="7"/>
+    </row>
+    <row r="27" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="7"/>
+      <c r="C27" s="73" t="s">
+        <v>156</v>
+      </c>
+      <c r="I27" s="7"/>
+    </row>
+    <row r="28" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="7"/>
+      <c r="C28" s="171" t="s">
+        <v>157</v>
+      </c>
+      <c r="I28" s="7"/>
+    </row>
+    <row r="29" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="7"/>
+      <c r="C29" s="73"/>
+      <c r="I29" s="7"/>
+    </row>
+    <row r="30" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="7"/>
+      <c r="C30" s="73"/>
+      <c r="I30" s="7"/>
+    </row>
+    <row r="31" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="7"/>
+      <c r="C31" s="73"/>
+      <c r="I31" s="7"/>
+    </row>
+    <row r="32" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="7"/>
+      <c r="I32" s="7"/>
+    </row>
+    <row r="33" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="7"/>
+      <c r="I33" s="7"/>
+    </row>
+    <row r="34" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="7"/>
+      <c r="I34" s="7"/>
+    </row>
+    <row r="35" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="7"/>
+      <c r="I35" s="7"/>
+    </row>
+    <row r="36" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="7"/>
+      <c r="I36" s="7"/>
+    </row>
+    <row r="37" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="7"/>
+      <c r="I37" s="7"/>
+    </row>
+    <row r="38" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="7"/>
+      <c r="I38" s="7"/>
+    </row>
+    <row r="39" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="7"/>
+      <c r="I39" s="7"/>
+    </row>
+    <row r="40" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="7"/>
+      <c r="I40" s="7"/>
+    </row>
+    <row r="41" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="7"/>
+      <c r="I41" s="7"/>
+    </row>
+    <row r="42" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="7"/>
+      <c r="I42" s="7"/>
+    </row>
+    <row r="43" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="7"/>
+      <c r="I43" s="7"/>
+    </row>
+    <row r="44" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="7"/>
+      <c r="I44" s="7"/>
+    </row>
+    <row r="45" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="7"/>
+      <c r="I45" s="7"/>
+    </row>
+    <row r="46" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="7"/>
+      <c r="I46" s="7"/>
+    </row>
+    <row r="47" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="7"/>
+      <c r="I47" s="7"/>
+    </row>
+    <row r="48" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="7"/>
+      <c r="I48" s="7"/>
+    </row>
+    <row r="49" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="7"/>
+      <c r="I49" s="7"/>
+    </row>
+    <row r="50" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="7"/>
+      <c r="I50" s="7"/>
+    </row>
+    <row r="51" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="7"/>
+      <c r="I51" s="7"/>
+    </row>
+    <row r="52" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="7"/>
+      <c r="I52" s="7"/>
+    </row>
+    <row r="53" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="7"/>
+      <c r="I53" s="7"/>
+    </row>
+    <row r="54" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="7"/>
+      <c r="I54" s="7"/>
+    </row>
+    <row r="55" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="7"/>
+      <c r="I55" s="7"/>
+    </row>
+    <row r="56" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="7"/>
+      <c r="I56" s="7"/>
+    </row>
+    <row r="57" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="7"/>
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="7"/>
+      <c r="I58" s="7"/>
+    </row>
+    <row r="59" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="7"/>
+      <c r="I59" s="7"/>
+    </row>
+    <row r="60" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="7"/>
+      <c r="I60" s="7"/>
+    </row>
+    <row r="61" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="7"/>
+      <c r="I61" s="7"/>
+    </row>
+    <row r="62" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="7"/>
+      <c r="I62" s="7"/>
+    </row>
+    <row r="63" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="7"/>
+      <c r="I63" s="7"/>
+    </row>
+    <row r="64" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="7"/>
+      <c r="I64" s="7"/>
+    </row>
+    <row r="65" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="7"/>
+      <c r="I65" s="7"/>
+    </row>
+    <row r="66" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="7"/>
+      <c r="I66" s="7"/>
+    </row>
+    <row r="67" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="7"/>
+      <c r="I67" s="7"/>
+    </row>
+    <row r="68" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="7"/>
+      <c r="I68" s="7"/>
+    </row>
+    <row r="69" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B69" s="7"/>
+      <c r="I69" s="7"/>
+    </row>
+    <row r="70" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B70" s="7"/>
+      <c r="I70" s="7"/>
+    </row>
+    <row r="71" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" s="7"/>
+      <c r="I71" s="7"/>
+    </row>
+    <row r="72" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B72" s="7"/>
+      <c r="I72" s="7"/>
+    </row>
+    <row r="73" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B73" s="7"/>
+      <c r="I73" s="7"/>
+    </row>
+    <row r="74" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B74" s="7"/>
+      <c r="I74" s="7"/>
+    </row>
+    <row r="75" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="7"/>
+      <c r="I75" s="7"/>
+    </row>
+    <row r="76" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="7"/>
+      <c r="I76" s="7"/>
+    </row>
+    <row r="77" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="7"/>
+      <c r="I77" s="7"/>
+    </row>
+    <row r="78" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="7"/>
+      <c r="I78" s="7"/>
+    </row>
+    <row r="79" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="7"/>
+      <c r="I79" s="7"/>
+    </row>
+    <row r="80" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="7"/>
+      <c r="I80" s="7"/>
+    </row>
+    <row r="81" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="7"/>
+      <c r="I81" s="7"/>
+    </row>
+    <row r="82" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="7"/>
+      <c r="I82" s="7"/>
+    </row>
+    <row r="83" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="7"/>
+      <c r="I83" s="7"/>
+    </row>
+    <row r="84" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="7"/>
+      <c r="I84" s="7"/>
+    </row>
+    <row r="85" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="7"/>
+      <c r="I85" s="7"/>
+    </row>
+    <row r="86" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B86" s="7"/>
+      <c r="I86" s="7"/>
+    </row>
+    <row r="87" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B87" s="7"/>
+      <c r="I87" s="7"/>
+    </row>
+    <row r="88" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B88" s="7"/>
+      <c r="I88" s="7"/>
+    </row>
+    <row r="89" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B89" s="7"/>
+      <c r="I89" s="7"/>
+    </row>
+    <row r="90" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B90" s="7"/>
+      <c r="I90" s="7"/>
+    </row>
+    <row r="91" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B91" s="7"/>
+      <c r="I91" s="7"/>
+    </row>
+    <row r="92" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B92" s="7"/>
+      <c r="I92" s="7"/>
+    </row>
+    <row r="93" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B93" s="7"/>
+      <c r="I93" s="7"/>
+    </row>
+    <row r="94" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B94" s="7"/>
+      <c r="I94" s="7"/>
+    </row>
+    <row r="95" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B95" s="7"/>
+      <c r="I95" s="7"/>
+    </row>
+    <row r="96" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B96" s="7"/>
+      <c r="I96" s="7"/>
+    </row>
+    <row r="97" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B97" s="7"/>
+      <c r="I97" s="7"/>
+    </row>
+    <row r="98" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B98" s="7"/>
+      <c r="I98" s="7"/>
+    </row>
+    <row r="99" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B99" s="7"/>
+      <c r="I99" s="7"/>
+    </row>
+    <row r="100" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B100" s="7"/>
+      <c r="I100" s="7"/>
+    </row>
+    <row r="101" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B101" s="7"/>
+      <c r="I101" s="7"/>
+    </row>
+    <row r="102" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B102" s="7"/>
+      <c r="I102" s="7"/>
+    </row>
+    <row r="103" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B103" s="7"/>
+      <c r="I103" s="7"/>
+    </row>
+    <row r="104" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B104" s="7"/>
+      <c r="I104" s="7"/>
+    </row>
+    <row r="105" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B105" s="7"/>
+      <c r="I105" s="7"/>
+    </row>
+    <row r="106" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B106" s="7"/>
+      <c r="I106" s="7"/>
+    </row>
+    <row r="107" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B107" s="7"/>
+      <c r="I107" s="7"/>
+    </row>
+    <row r="108" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B108" s="7"/>
+      <c r="I108" s="7"/>
+    </row>
+    <row r="109" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B109" s="7"/>
+      <c r="I109" s="7"/>
+    </row>
+    <row r="110" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B110" s="7"/>
+      <c r="I110" s="7"/>
+    </row>
+    <row r="111" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B111" s="7"/>
+      <c r="I111" s="7"/>
+    </row>
+    <row r="112" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B112" s="7"/>
+      <c r="I112" s="7"/>
+    </row>
+    <row r="113" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B113" s="7"/>
+      <c r="I113" s="7"/>
+    </row>
+    <row r="114" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B114" s="7"/>
+      <c r="I114" s="7"/>
+    </row>
+    <row r="115" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B115" s="7"/>
+      <c r="I115" s="7"/>
+    </row>
+    <row r="116" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B116" s="7"/>
+      <c r="I116" s="7"/>
+    </row>
+    <row r="117" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B117" s="7"/>
+      <c r="I117" s="7"/>
+    </row>
+    <row r="118" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B118" s="7"/>
+      <c r="I118" s="7"/>
+    </row>
+    <row r="119" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B119" s="7"/>
+      <c r="I119" s="7"/>
+    </row>
+    <row r="120" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B120" s="7"/>
+      <c r="I120" s="7"/>
+    </row>
+    <row r="121" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B121" s="7"/>
+      <c r="I121" s="7"/>
+    </row>
+    <row r="122" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B122" s="7"/>
+      <c r="I122" s="7"/>
+    </row>
+    <row r="123" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B123" s="7"/>
+      <c r="I123" s="7"/>
+    </row>
+    <row r="124" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B124" s="7"/>
+      <c r="I124" s="7"/>
+    </row>
+    <row r="125" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B125" s="7"/>
+      <c r="I125" s="7"/>
+    </row>
+    <row r="126" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B126" s="7"/>
+      <c r="I126" s="7"/>
+    </row>
+    <row r="127" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B127" s="7"/>
+      <c r="I127" s="7"/>
+    </row>
+    <row r="128" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B128" s="7"/>
+      <c r="I128" s="7"/>
+    </row>
+    <row r="129" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B129" s="7"/>
+      <c r="I129" s="7"/>
+    </row>
+    <row r="130" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B130" s="7"/>
+      <c r="I130" s="7"/>
+    </row>
+    <row r="131" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B131" s="7"/>
+      <c r="I131" s="7"/>
+    </row>
+    <row r="132" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B132" s="7"/>
+      <c r="I132" s="7"/>
+    </row>
+    <row r="133" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B133" s="7"/>
+      <c r="I133" s="7"/>
+    </row>
+    <row r="134" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B134" s="7"/>
+      <c r="I134" s="7"/>
+    </row>
+    <row r="135" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B135" s="7"/>
+      <c r="I135" s="7"/>
+    </row>
+    <row r="136" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B136" s="7"/>
+      <c r="I136" s="7"/>
+    </row>
+    <row r="137" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B137" s="7"/>
+      <c r="I137" s="7"/>
+    </row>
+    <row r="138" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B138" s="7"/>
+      <c r="I138" s="7"/>
+    </row>
+    <row r="139" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B139" s="7"/>
+      <c r="I139" s="7"/>
+    </row>
+    <row r="140" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B140" s="7"/>
+      <c r="I140" s="7"/>
+    </row>
+    <row r="141" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B141" s="7"/>
+      <c r="I141" s="7"/>
+    </row>
+    <row r="142" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B142" s="7"/>
+      <c r="I142" s="7"/>
+    </row>
+    <row r="143" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B143" s="7"/>
+      <c r="I143" s="7"/>
+    </row>
+    <row r="144" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B144" s="7"/>
+      <c r="I144" s="7"/>
+    </row>
+    <row r="145" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B145" s="7"/>
+      <c r="I145" s="7"/>
+    </row>
+    <row r="146" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B146" s="7"/>
+      <c r="I146" s="7"/>
+    </row>
+    <row r="147" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B147" s="7"/>
+      <c r="I147" s="7"/>
+    </row>
+    <row r="148" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B148" s="7"/>
+      <c r="I148" s="7"/>
+    </row>
+    <row r="149" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B149" s="7"/>
+      <c r="I149" s="7"/>
+    </row>
+    <row r="150" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B150" s="7"/>
+      <c r="I150" s="7"/>
+    </row>
+    <row r="151" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B151" s="7"/>
+      <c r="I151" s="7"/>
+    </row>
+    <row r="152" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B152" s="7"/>
+      <c r="I152" s="7"/>
+    </row>
+    <row r="153" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B153" s="7"/>
+      <c r="I153" s="7"/>
+    </row>
+    <row r="154" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B154" s="7"/>
+      <c r="I154" s="7"/>
+    </row>
+    <row r="155" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B155" s="7"/>
+      <c r="I155" s="7"/>
+    </row>
+    <row r="156" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B156" s="7"/>
+      <c r="I156" s="7"/>
+    </row>
+    <row r="157" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B157" s="7"/>
+      <c r="I157" s="7"/>
+    </row>
+    <row r="158" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B158" s="7"/>
+      <c r="I158" s="7"/>
+    </row>
+    <row r="159" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B159" s="7"/>
+      <c r="I159" s="7"/>
+    </row>
+    <row r="160" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B160" s="7"/>
+      <c r="I160" s="7"/>
+    </row>
+    <row r="161" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B161" s="7"/>
+      <c r="I161" s="7"/>
+    </row>
+    <row r="162" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B162" s="7"/>
+      <c r="I162" s="7"/>
+    </row>
+    <row r="163" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B163" s="7"/>
+      <c r="I163" s="7"/>
+    </row>
+    <row r="164" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B164" s="7"/>
+      <c r="I164" s="7"/>
+    </row>
+    <row r="165" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B165" s="7"/>
+      <c r="I165" s="7"/>
+    </row>
+    <row r="166" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B166" s="7"/>
+      <c r="I166" s="7"/>
+    </row>
+    <row r="167" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B167" s="7"/>
+      <c r="I167" s="7"/>
+    </row>
+    <row r="168" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B168" s="7"/>
+      <c r="I168" s="7"/>
+    </row>
+    <row r="169" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B169" s="7"/>
+      <c r="I169" s="7"/>
+    </row>
+    <row r="170" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B170" s="7"/>
+      <c r="I170" s="7"/>
+    </row>
+    <row r="171" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B171" s="7"/>
+      <c r="I171" s="7"/>
+    </row>
+    <row r="172" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B172" s="7"/>
+      <c r="I172" s="7"/>
+    </row>
+    <row r="173" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B173" s="7"/>
+      <c r="I173" s="7"/>
+    </row>
+    <row r="174" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B174" s="7"/>
+      <c r="I174" s="7"/>
+    </row>
+    <row r="175" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B175" s="7"/>
+      <c r="I175" s="7"/>
+    </row>
+    <row r="176" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B176" s="7"/>
+      <c r="I176" s="7"/>
+    </row>
+    <row r="177" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B177" s="7"/>
+      <c r="I177" s="7"/>
+    </row>
+    <row r="178" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B178" s="7"/>
+      <c r="I178" s="7"/>
+    </row>
+    <row r="179" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B179" s="7"/>
+      <c r="I179" s="7"/>
+    </row>
+    <row r="180" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B180" s="7"/>
+      <c r="I180" s="7"/>
+    </row>
+    <row r="181" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B181" s="7"/>
+      <c r="I181" s="7"/>
+    </row>
+    <row r="182" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B182" s="7"/>
+      <c r="I182" s="7"/>
+    </row>
+    <row r="183" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B183" s="7"/>
+      <c r="I183" s="7"/>
+    </row>
+    <row r="184" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B184" s="7"/>
+      <c r="I184" s="7"/>
+    </row>
+    <row r="185" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B185" s="7"/>
+      <c r="I185" s="7"/>
+    </row>
+    <row r="186" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B186" s="7"/>
+      <c r="I186" s="7"/>
+    </row>
+    <row r="187" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B187" s="7"/>
+      <c r="I187" s="7"/>
+    </row>
+    <row r="188" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B188" s="7"/>
+      <c r="I188" s="7"/>
+    </row>
+    <row r="189" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B189" s="7"/>
+      <c r="I189" s="7"/>
+    </row>
+    <row r="190" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B190" s="7"/>
+      <c r="I190" s="7"/>
+    </row>
+    <row r="191" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B191" s="7"/>
+      <c r="I191" s="7"/>
+    </row>
+    <row r="192" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B192" s="7"/>
+      <c r="I192" s="7"/>
+    </row>
+    <row r="193" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B193" s="7"/>
+      <c r="I193" s="7"/>
+    </row>
+    <row r="194" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B194" s="7"/>
+      <c r="I194" s="7"/>
+    </row>
+    <row r="195" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B195" s="7"/>
+      <c r="I195" s="7"/>
+    </row>
+    <row r="196" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B196" s="7"/>
+      <c r="I196" s="7"/>
+    </row>
+    <row r="197" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B197" s="7"/>
+      <c r="I197" s="7"/>
+    </row>
+    <row r="198" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B198" s="7"/>
+      <c r="I198" s="7"/>
+    </row>
+    <row r="199" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B199" s="7"/>
+      <c r="I199" s="7"/>
+    </row>
+    <row r="200" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B200" s="7"/>
+      <c r="I200" s="7"/>
+    </row>
+    <row r="201" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B201" s="7"/>
+      <c r="I201" s="7"/>
+    </row>
+    <row r="202" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B202" s="7"/>
+      <c r="I202" s="7"/>
+    </row>
+    <row r="203" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B203" s="7"/>
+      <c r="I203" s="7"/>
+    </row>
+    <row r="204" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B204" s="7"/>
+      <c r="I204" s="7"/>
+    </row>
+    <row r="205" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B205" s="7"/>
+      <c r="I205" s="7"/>
+    </row>
+    <row r="206" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B206" s="7"/>
+      <c r="I206" s="7"/>
+    </row>
+    <row r="207" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B207" s="7"/>
+      <c r="I207" s="7"/>
+    </row>
+    <row r="208" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B208" s="7"/>
+      <c r="I208" s="7"/>
+    </row>
+    <row r="209" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B209" s="7"/>
+      <c r="I209" s="7"/>
+    </row>
+    <row r="210" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B210" s="7"/>
+      <c r="I210" s="7"/>
+    </row>
+    <row r="211" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B211" s="7"/>
+      <c r="I211" s="7"/>
+    </row>
+    <row r="212" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B212" s="7"/>
+      <c r="I212" s="7"/>
+    </row>
+    <row r="213" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B213" s="7"/>
+      <c r="I213" s="7"/>
+    </row>
+    <row r="214" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B214" s="7"/>
+      <c r="I214" s="7"/>
+    </row>
+    <row r="215" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B215" s="7"/>
+      <c r="I215" s="7"/>
+    </row>
+    <row r="216" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B216" s="7"/>
+      <c r="I216" s="7"/>
+    </row>
+    <row r="217" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B217" s="7"/>
+      <c r="I217" s="7"/>
+    </row>
+    <row r="218" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B218" s="7"/>
+      <c r="I218" s="7"/>
+    </row>
+    <row r="219" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B219" s="7"/>
+      <c r="I219" s="7"/>
+    </row>
+    <row r="220" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B220" s="7"/>
+      <c r="I220" s="7"/>
+    </row>
+    <row r="221" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B221" s="7"/>
+      <c r="I221" s="7"/>
+    </row>
+    <row r="222" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B222" s="7"/>
+      <c r="I222" s="7"/>
+    </row>
+    <row r="223" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B223" s="7"/>
+      <c r="I223" s="7"/>
+    </row>
+    <row r="224" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B224" s="7"/>
+      <c r="I224" s="7"/>
+    </row>
+    <row r="225" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B225" s="7"/>
+      <c r="I225" s="7"/>
+    </row>
+    <row r="226" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B226" s="7"/>
+      <c r="I226" s="7"/>
+    </row>
+    <row r="227" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B227" s="7"/>
+      <c r="I227" s="7"/>
+    </row>
+    <row r="228" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B228" s="7"/>
+      <c r="I228" s="7"/>
+    </row>
+    <row r="229" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B229" s="7"/>
+      <c r="I229" s="7"/>
+    </row>
+    <row r="230" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B230" s="7"/>
+      <c r="I230" s="7"/>
+    </row>
+    <row r="231" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B231" s="7"/>
+      <c r="I231" s="7"/>
+    </row>
+    <row r="232" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B232" s="7"/>
+      <c r="I232" s="7"/>
+    </row>
+    <row r="233" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B233" s="7"/>
+      <c r="I233" s="7"/>
+    </row>
+    <row r="234" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B234" s="7"/>
+      <c r="I234" s="7"/>
+    </row>
+    <row r="235" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B235" s="7"/>
+      <c r="I235" s="7"/>
+    </row>
+    <row r="236" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B236" s="7"/>
+      <c r="I236" s="7"/>
+    </row>
+    <row r="237" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B237" s="7"/>
+      <c r="I237" s="7"/>
+    </row>
+    <row r="238" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B238" s="7"/>
+      <c r="I238" s="7"/>
+    </row>
+    <row r="239" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B239" s="7"/>
+      <c r="I239" s="7"/>
+    </row>
+    <row r="240" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B240" s="7"/>
+      <c r="I240" s="7"/>
+    </row>
+    <row r="241" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B241" s="7"/>
+      <c r="I241" s="7"/>
+    </row>
+    <row r="242" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B242" s="7"/>
+      <c r="I242" s="7"/>
+    </row>
+    <row r="243" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B243" s="7"/>
+      <c r="I243" s="7"/>
+    </row>
+    <row r="244" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B244" s="7"/>
+      <c r="I244" s="7"/>
+    </row>
+    <row r="245" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B245" s="7"/>
+      <c r="I245" s="7"/>
+    </row>
+    <row r="246" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B246" s="7"/>
+      <c r="I246" s="7"/>
+    </row>
+    <row r="247" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B247" s="7"/>
+      <c r="I247" s="7"/>
+    </row>
+    <row r="248" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B248" s="7"/>
+      <c r="I248" s="7"/>
+    </row>
+    <row r="249" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B249" s="7"/>
+      <c r="I249" s="7"/>
+    </row>
+    <row r="250" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B250" s="7"/>
+      <c r="I250" s="7"/>
+    </row>
+    <row r="251" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B251" s="7"/>
+      <c r="I251" s="7"/>
+    </row>
+    <row r="252" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B252" s="7"/>
+      <c r="I252" s="7"/>
+    </row>
+    <row r="253" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B253" s="7"/>
+      <c r="I253" s="7"/>
+    </row>
+    <row r="254" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B254" s="7"/>
+      <c r="I254" s="7"/>
+    </row>
+    <row r="255" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B255" s="7"/>
+      <c r="I255" s="7"/>
+    </row>
+    <row r="256" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B256" s="7"/>
+      <c r="I256" s="7"/>
+    </row>
+    <row r="257" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B257" s="7"/>
+      <c r="I257" s="7"/>
+    </row>
+    <row r="258" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B258" s="7"/>
+      <c r="I258" s="7"/>
+    </row>
+    <row r="259" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B259" s="7"/>
+      <c r="I259" s="7"/>
+    </row>
+    <row r="260" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B260" s="7"/>
+      <c r="I260" s="7"/>
+    </row>
+    <row r="261" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B261" s="7"/>
+      <c r="I261" s="7"/>
+    </row>
+    <row r="262" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B262" s="7"/>
+      <c r="I262" s="7"/>
+    </row>
+    <row r="263" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B263" s="7"/>
+      <c r="I263" s="7"/>
+    </row>
+    <row r="264" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B264" s="7"/>
+      <c r="I264" s="7"/>
+    </row>
+    <row r="265" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B265" s="7"/>
+      <c r="I265" s="7"/>
+    </row>
+    <row r="266" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B266" s="7"/>
+      <c r="I266" s="7"/>
+    </row>
+    <row r="267" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B267" s="7"/>
+      <c r="I267" s="7"/>
+    </row>
+    <row r="268" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B268" s="7"/>
+      <c r="I268" s="7"/>
+    </row>
+    <row r="269" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B269" s="7"/>
+      <c r="I269" s="7"/>
+    </row>
+    <row r="270" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B270" s="7"/>
+      <c r="I270" s="7"/>
+    </row>
+    <row r="271" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B271" s="7"/>
+      <c r="I271" s="7"/>
+    </row>
+    <row r="272" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B272" s="7"/>
+      <c r="I272" s="7"/>
+    </row>
+    <row r="273" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B273" s="7"/>
+      <c r="I273" s="7"/>
+    </row>
+    <row r="274" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B274" s="7"/>
+      <c r="I274" s="7"/>
+    </row>
+    <row r="275" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B275" s="7"/>
+      <c r="I275" s="7"/>
+    </row>
+    <row r="276" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B276" s="7"/>
+      <c r="I276" s="7"/>
+    </row>
+    <row r="277" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B277" s="7"/>
+      <c r="I277" s="7"/>
+    </row>
+    <row r="278" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B278" s="7"/>
+      <c r="I278" s="7"/>
+    </row>
+    <row r="279" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B279" s="7"/>
+      <c r="I279" s="7"/>
+    </row>
+    <row r="280" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B280" s="7"/>
+      <c r="I280" s="7"/>
+    </row>
+    <row r="281" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B281" s="7"/>
+      <c r="I281" s="7"/>
+    </row>
+    <row r="282" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B282" s="7"/>
+      <c r="I282" s="7"/>
+    </row>
+    <row r="283" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B283" s="7"/>
+      <c r="I283" s="7"/>
+    </row>
+    <row r="284" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B284" s="7"/>
+      <c r="I284" s="7"/>
+    </row>
+    <row r="285" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B285" s="7"/>
+      <c r="I285" s="7"/>
+    </row>
+    <row r="286" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B286" s="7"/>
+      <c r="I286" s="7"/>
+    </row>
+    <row r="287" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B287" s="7"/>
+      <c r="I287" s="7"/>
+    </row>
+    <row r="288" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B288" s="7"/>
+      <c r="I288" s="7"/>
+    </row>
+    <row r="289" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B289" s="7"/>
+      <c r="I289" s="7"/>
+    </row>
+    <row r="290" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B290" s="7"/>
+      <c r="I290" s="7"/>
+    </row>
+    <row r="291" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B291" s="7"/>
+      <c r="I291" s="7"/>
+    </row>
+    <row r="292" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B292" s="7"/>
+      <c r="I292" s="7"/>
+    </row>
+    <row r="293" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B293" s="7"/>
+      <c r="I293" s="7"/>
+    </row>
+    <row r="294" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B294" s="7"/>
+      <c r="I294" s="7"/>
+    </row>
+    <row r="295" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B295" s="7"/>
+      <c r="I295" s="7"/>
+    </row>
+    <row r="296" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B296" s="7"/>
+      <c r="I296" s="7"/>
+    </row>
+    <row r="297" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B297" s="7"/>
+      <c r="I297" s="7"/>
+    </row>
+    <row r="298" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B298" s="7"/>
+      <c r="I298" s="7"/>
+    </row>
+    <row r="299" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B299" s="7"/>
+      <c r="I299" s="7"/>
+    </row>
+    <row r="300" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B300" s="7"/>
+      <c r="I300" s="7"/>
+    </row>
+    <row r="301" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B301" s="7"/>
+      <c r="I301" s="7"/>
+    </row>
+    <row r="302" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B302" s="7"/>
+      <c r="I302" s="7"/>
+    </row>
+    <row r="303" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B303" s="7"/>
+      <c r="I303" s="7"/>
+    </row>
+    <row r="304" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B304" s="7"/>
+      <c r="I304" s="7"/>
+    </row>
+    <row r="305" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B305" s="7"/>
+      <c r="I305" s="7"/>
+    </row>
+    <row r="306" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B306" s="7"/>
+      <c r="I306" s="7"/>
+    </row>
+    <row r="307" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B307" s="7"/>
+      <c r="I307" s="7"/>
+    </row>
+    <row r="308" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B308" s="7"/>
+      <c r="I308" s="7"/>
+    </row>
+    <row r="309" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B309" s="7"/>
+      <c r="I309" s="7"/>
+    </row>
+    <row r="310" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B310" s="7"/>
+      <c r="I310" s="7"/>
+    </row>
+    <row r="311" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B311" s="7"/>
+      <c r="I311" s="7"/>
+    </row>
+    <row r="312" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B312" s="7"/>
+      <c r="I312" s="7"/>
+    </row>
+    <row r="313" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B313" s="7"/>
+      <c r="I313" s="7"/>
+    </row>
+    <row r="314" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B314" s="7"/>
+      <c r="I314" s="7"/>
+    </row>
+    <row r="315" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B315" s="7"/>
+      <c r="I315" s="7"/>
+    </row>
+    <row r="316" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B316" s="7"/>
+      <c r="I316" s="7"/>
+    </row>
+    <row r="317" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B317" s="7"/>
+      <c r="I317" s="7"/>
+    </row>
+    <row r="318" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B318" s="7"/>
+      <c r="I318" s="7"/>
+    </row>
+    <row r="319" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B319" s="7"/>
+      <c r="I319" s="7"/>
+    </row>
+    <row r="320" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B320" s="7"/>
+      <c r="I320" s="7"/>
+    </row>
+    <row r="321" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B321" s="7"/>
+      <c r="I321" s="7"/>
+    </row>
+    <row r="322" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B322" s="7"/>
+      <c r="I322" s="7"/>
+    </row>
+    <row r="323" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B323" s="7"/>
+      <c r="I323" s="7"/>
+    </row>
+    <row r="324" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B324" s="7"/>
+      <c r="I324" s="7"/>
+    </row>
+    <row r="325" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B325" s="7"/>
+      <c r="I325" s="7"/>
+    </row>
+    <row r="326" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B326" s="7"/>
+      <c r="I326" s="7"/>
+    </row>
+    <row r="327" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B327" s="7"/>
+      <c r="I327" s="7"/>
+    </row>
+    <row r="328" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B328" s="7"/>
+      <c r="I328" s="7"/>
+    </row>
+    <row r="329" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B329" s="7"/>
+      <c r="I329" s="7"/>
+    </row>
+    <row r="330" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B330" s="7"/>
+      <c r="I330" s="7"/>
+    </row>
+    <row r="331" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B331" s="7"/>
+      <c r="I331" s="7"/>
+    </row>
+    <row r="332" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B332" s="7"/>
+      <c r="I332" s="7"/>
+    </row>
+    <row r="333" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B333" s="7"/>
+      <c r="I333" s="7"/>
+    </row>
+    <row r="334" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B334" s="7"/>
+      <c r="I334" s="7"/>
+    </row>
+    <row r="335" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B335" s="7"/>
+      <c r="I335" s="7"/>
+    </row>
+    <row r="336" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B336" s="7"/>
+      <c r="I336" s="7"/>
+    </row>
+    <row r="337" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B337" s="7"/>
+      <c r="I337" s="7"/>
+    </row>
+    <row r="338" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B338" s="7"/>
+      <c r="I338" s="7"/>
+    </row>
+    <row r="339" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B339" s="7"/>
+      <c r="I339" s="7"/>
+    </row>
+    <row r="340" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B340" s="7"/>
+      <c r="I340" s="7"/>
+    </row>
+    <row r="341" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B341" s="7"/>
+      <c r="I341" s="7"/>
+    </row>
+    <row r="342" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B342" s="7"/>
+      <c r="I342" s="7"/>
+    </row>
+    <row r="343" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B343" s="7"/>
+      <c r="I343" s="7"/>
+    </row>
+    <row r="344" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B344" s="7"/>
+      <c r="I344" s="7"/>
+    </row>
+    <row r="345" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B345" s="7"/>
+      <c r="I345" s="7"/>
+    </row>
+    <row r="346" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B346" s="7"/>
+      <c r="I346" s="7"/>
+    </row>
+    <row r="347" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B347" s="7"/>
+      <c r="I347" s="7"/>
+    </row>
+    <row r="348" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B348" s="7"/>
+      <c r="I348" s="7"/>
+    </row>
+    <row r="349" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B349" s="7"/>
+      <c r="I349" s="7"/>
+    </row>
+    <row r="350" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B350" s="7"/>
+      <c r="I350" s="7"/>
+    </row>
+    <row r="351" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B351" s="7"/>
+      <c r="I351" s="7"/>
+    </row>
+    <row r="352" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B352" s="7"/>
+      <c r="I352" s="7"/>
+    </row>
+    <row r="353" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B353" s="7"/>
+      <c r="I353" s="7"/>
+    </row>
+    <row r="354" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B354" s="7"/>
+      <c r="I354" s="7"/>
+    </row>
+    <row r="355" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B355" s="7"/>
+      <c r="I355" s="7"/>
+    </row>
+    <row r="356" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B356" s="7"/>
+      <c r="I356" s="7"/>
+    </row>
+    <row r="357" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B357" s="7"/>
+      <c r="I357" s="7"/>
+    </row>
+    <row r="358" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B358" s="7"/>
+      <c r="I358" s="7"/>
+    </row>
+    <row r="359" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B359" s="7"/>
+      <c r="I359" s="7"/>
+    </row>
+    <row r="360" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B360" s="7"/>
+      <c r="I360" s="7"/>
+    </row>
+    <row r="361" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B361" s="7"/>
+      <c r="I361" s="7"/>
+    </row>
+    <row r="362" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B362" s="7"/>
+      <c r="I362" s="7"/>
+    </row>
+    <row r="363" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B363" s="7"/>
+      <c r="I363" s="7"/>
+    </row>
+    <row r="364" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B364" s="7"/>
+      <c r="I364" s="7"/>
+    </row>
+    <row r="365" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B365" s="7"/>
+      <c r="I365" s="7"/>
+    </row>
+    <row r="366" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B366" s="7"/>
+      <c r="I366" s="7"/>
+    </row>
+    <row r="367" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B367" s="7"/>
+      <c r="I367" s="7"/>
+    </row>
+    <row r="368" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B368" s="7"/>
+      <c r="I368" s="7"/>
+    </row>
+    <row r="369" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B369" s="7"/>
+      <c r="I369" s="7"/>
+    </row>
+    <row r="370" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B370" s="7"/>
+      <c r="I370" s="7"/>
+    </row>
+    <row r="371" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B371" s="7"/>
+      <c r="I371" s="7"/>
+    </row>
+    <row r="372" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B372" s="7"/>
+      <c r="I372" s="7"/>
+    </row>
+    <row r="373" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B373" s="7"/>
+      <c r="I373" s="7"/>
+    </row>
+    <row r="374" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B374" s="7"/>
+      <c r="I374" s="7"/>
+    </row>
+    <row r="375" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B375" s="7"/>
+      <c r="I375" s="7"/>
+    </row>
+    <row r="376" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B376" s="7"/>
+      <c r="I376" s="7"/>
+    </row>
+    <row r="377" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B377" s="7"/>
+      <c r="I377" s="7"/>
+    </row>
+    <row r="378" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B378" s="7"/>
+      <c r="I378" s="7"/>
+    </row>
+    <row r="379" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B379" s="7"/>
+      <c r="I379" s="7"/>
+    </row>
+    <row r="380" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B380" s="7"/>
+      <c r="I380" s="7"/>
+    </row>
+    <row r="381" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B381" s="7"/>
+      <c r="I381" s="7"/>
+    </row>
+    <row r="382" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B382" s="7"/>
+      <c r="I382" s="7"/>
+    </row>
+    <row r="383" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B383" s="7"/>
+      <c r="I383" s="7"/>
+    </row>
+    <row r="384" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B384" s="7"/>
+      <c r="I384" s="7"/>
+    </row>
+    <row r="385" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B385" s="7"/>
+      <c r="I385" s="7"/>
+    </row>
+    <row r="386" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B386" s="7"/>
+      <c r="I386" s="7"/>
+    </row>
+    <row r="387" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B387" s="7"/>
+      <c r="I387" s="7"/>
+    </row>
+    <row r="388" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B388" s="7"/>
+      <c r="I388" s="7"/>
+    </row>
+    <row r="389" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B389" s="7"/>
+      <c r="I389" s="7"/>
+    </row>
+    <row r="390" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B390" s="7"/>
+      <c r="I390" s="7"/>
+    </row>
+    <row r="391" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B391" s="7"/>
+      <c r="I391" s="7"/>
+    </row>
+    <row r="392" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B392" s="7"/>
+      <c r="I392" s="7"/>
+    </row>
+    <row r="393" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B393" s="7"/>
+      <c r="I393" s="7"/>
+    </row>
+    <row r="394" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B394" s="7"/>
+      <c r="I394" s="7"/>
+    </row>
+    <row r="395" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B395" s="7"/>
+      <c r="I395" s="7"/>
+    </row>
+    <row r="396" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B396" s="7"/>
+      <c r="I396" s="7"/>
+    </row>
+    <row r="397" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B397" s="7"/>
+      <c r="I397" s="7"/>
+    </row>
+    <row r="398" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B398" s="7"/>
+      <c r="I398" s="7"/>
+    </row>
+    <row r="399" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B399" s="7"/>
+      <c r="I399" s="7"/>
+    </row>
+    <row r="400" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B400" s="7"/>
+      <c r="I400" s="7"/>
+    </row>
+    <row r="401" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B401" s="7"/>
+      <c r="I401" s="7"/>
+    </row>
+    <row r="402" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B402" s="7"/>
+      <c r="I402" s="7"/>
+    </row>
+    <row r="403" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B403" s="7"/>
+      <c r="I403" s="7"/>
+    </row>
+    <row r="404" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B404" s="7"/>
+      <c r="I404" s="7"/>
+    </row>
+    <row r="405" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B405" s="7"/>
+      <c r="I405" s="7"/>
+    </row>
+    <row r="406" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B406" s="7"/>
+      <c r="I406" s="7"/>
+    </row>
+    <row r="407" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B407" s="7"/>
+      <c r="I407" s="7"/>
+    </row>
+    <row r="408" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B408" s="7"/>
+      <c r="I408" s="7"/>
+    </row>
+    <row r="409" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B409" s="7"/>
+      <c r="I409" s="7"/>
+    </row>
+    <row r="410" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B410" s="7"/>
+      <c r="I410" s="7"/>
+    </row>
+    <row r="411" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B411" s="7"/>
+      <c r="I411" s="7"/>
+    </row>
+    <row r="412" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B412" s="7"/>
+      <c r="I412" s="7"/>
+    </row>
+    <row r="413" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B413" s="7"/>
+      <c r="I413" s="7"/>
+    </row>
+    <row r="414" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B414" s="7"/>
+      <c r="I414" s="7"/>
+    </row>
+    <row r="415" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B415" s="7"/>
+      <c r="I415" s="7"/>
+    </row>
+    <row r="416" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B416" s="7"/>
+      <c r="I416" s="7"/>
+    </row>
+    <row r="417" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B417" s="7"/>
+      <c r="I417" s="7"/>
+    </row>
+    <row r="418" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B418" s="7"/>
+      <c r="I418" s="7"/>
+    </row>
+    <row r="419" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B419" s="7"/>
+      <c r="I419" s="7"/>
+    </row>
+    <row r="420" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B420" s="7"/>
+      <c r="I420" s="7"/>
+    </row>
+    <row r="421" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B421" s="7"/>
+      <c r="I421" s="7"/>
+    </row>
+    <row r="422" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B422" s="7"/>
+      <c r="I422" s="7"/>
+    </row>
+    <row r="423" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B423" s="7"/>
+      <c r="I423" s="7"/>
+    </row>
+    <row r="424" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B424" s="7"/>
+      <c r="I424" s="7"/>
+    </row>
+    <row r="425" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B425" s="7"/>
+      <c r="I425" s="7"/>
+    </row>
+    <row r="426" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B426" s="7"/>
+      <c r="I426" s="7"/>
+    </row>
+    <row r="427" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B427" s="7"/>
+      <c r="I427" s="7"/>
+    </row>
+    <row r="428" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B428" s="7"/>
+      <c r="I428" s="7"/>
+    </row>
+    <row r="429" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B429" s="7"/>
+      <c r="I429" s="7"/>
+    </row>
+    <row r="430" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B430" s="7"/>
+      <c r="I430" s="7"/>
+    </row>
+    <row r="431" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B431" s="7"/>
+      <c r="I431" s="7"/>
+    </row>
+    <row r="432" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B432" s="7"/>
+      <c r="I432" s="7"/>
+    </row>
+    <row r="433" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B433" s="7"/>
+      <c r="I433" s="7"/>
+    </row>
+    <row r="434" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B434" s="7"/>
+      <c r="I434" s="7"/>
+    </row>
+    <row r="435" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B435" s="7"/>
+      <c r="I435" s="7"/>
+    </row>
+    <row r="436" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B436" s="7"/>
+      <c r="I436" s="7"/>
+    </row>
+    <row r="437" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B437" s="7"/>
+      <c r="I437" s="7"/>
+    </row>
+    <row r="438" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B438" s="7"/>
+      <c r="I438" s="7"/>
+    </row>
+    <row r="439" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B439" s="7"/>
+      <c r="I439" s="7"/>
+    </row>
+    <row r="440" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B440" s="7"/>
+      <c r="I440" s="7"/>
+    </row>
+    <row r="441" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B441" s="7"/>
+      <c r="I441" s="7"/>
+    </row>
+    <row r="442" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B442" s="7"/>
+      <c r="I442" s="7"/>
+    </row>
+    <row r="443" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B443" s="7"/>
+      <c r="I443" s="7"/>
+    </row>
+    <row r="444" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B444" s="7"/>
+      <c r="I444" s="7"/>
+    </row>
+    <row r="445" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B445" s="7"/>
+      <c r="I445" s="7"/>
+    </row>
+    <row r="446" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B446" s="7"/>
+      <c r="I446" s="7"/>
+    </row>
+    <row r="447" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B447" s="7"/>
+      <c r="I447" s="7"/>
+    </row>
+    <row r="448" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B448" s="7"/>
+      <c r="I448" s="7"/>
+    </row>
+    <row r="449" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B449" s="7"/>
+      <c r="I449" s="7"/>
+    </row>
+    <row r="450" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B450" s="7"/>
+      <c r="I450" s="7"/>
+    </row>
+    <row r="451" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B451" s="7"/>
+      <c r="I451" s="7"/>
+    </row>
+    <row r="452" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B452" s="7"/>
+      <c r="I452" s="7"/>
+    </row>
+    <row r="453" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B453" s="7"/>
+      <c r="I453" s="7"/>
+    </row>
+    <row r="454" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B454" s="7"/>
+      <c r="I454" s="7"/>
+    </row>
+    <row r="455" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B455" s="7"/>
+      <c r="I455" s="7"/>
+    </row>
+    <row r="456" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B456" s="7"/>
+      <c r="I456" s="7"/>
+    </row>
+    <row r="457" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B457" s="7"/>
+      <c r="I457" s="7"/>
+    </row>
+    <row r="458" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B458" s="7"/>
+      <c r="I458" s="7"/>
+    </row>
+    <row r="459" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B459" s="7"/>
+      <c r="I459" s="7"/>
+    </row>
+    <row r="460" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B460" s="7"/>
+      <c r="I460" s="7"/>
+    </row>
+    <row r="461" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B461" s="7"/>
+      <c r="I461" s="7"/>
+    </row>
+    <row r="462" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B462" s="7"/>
+      <c r="I462" s="7"/>
+    </row>
+    <row r="463" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B463" s="7"/>
+      <c r="I463" s="7"/>
+    </row>
+    <row r="464" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B464" s="7"/>
+      <c r="I464" s="7"/>
+    </row>
+    <row r="465" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B465" s="7"/>
+      <c r="I465" s="7"/>
+    </row>
+    <row r="466" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B466" s="7"/>
+      <c r="I466" s="7"/>
+    </row>
+    <row r="467" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B467" s="7"/>
+      <c r="I467" s="7"/>
+    </row>
+    <row r="468" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B468" s="7"/>
+      <c r="I468" s="7"/>
+    </row>
+    <row r="469" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B469" s="7"/>
+      <c r="I469" s="7"/>
+    </row>
+    <row r="470" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B470" s="7"/>
+      <c r="I470" s="7"/>
+    </row>
+    <row r="471" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B471" s="7"/>
+      <c r="I471" s="7"/>
+    </row>
+    <row r="472" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B472" s="7"/>
+      <c r="I472" s="7"/>
+    </row>
+    <row r="473" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B473" s="7"/>
+      <c r="I473" s="7"/>
+    </row>
+    <row r="474" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B474" s="7"/>
+      <c r="I474" s="7"/>
+    </row>
+    <row r="475" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B475" s="7"/>
+      <c r="I475" s="7"/>
+    </row>
+    <row r="476" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B476" s="7"/>
+      <c r="I476" s="7"/>
+    </row>
+    <row r="477" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B477" s="7"/>
+      <c r="I477" s="7"/>
+    </row>
+    <row r="478" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B478" s="7"/>
+      <c r="I478" s="7"/>
+    </row>
+    <row r="479" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B479" s="7"/>
+      <c r="I479" s="7"/>
+    </row>
+    <row r="480" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B480" s="7"/>
+      <c r="I480" s="7"/>
+    </row>
+    <row r="481" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B481" s="7"/>
+      <c r="I481" s="7"/>
+    </row>
+    <row r="482" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B482" s="7"/>
+      <c r="I482" s="7"/>
+    </row>
+    <row r="483" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B483" s="7"/>
+      <c r="I483" s="7"/>
+    </row>
+    <row r="484" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B484" s="7"/>
+      <c r="I484" s="7"/>
+    </row>
+    <row r="485" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B485" s="7"/>
+      <c r="I485" s="7"/>
+    </row>
+    <row r="486" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B486" s="7"/>
+      <c r="I486" s="7"/>
+    </row>
+    <row r="487" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B487" s="7"/>
+      <c r="I487" s="7"/>
+    </row>
+    <row r="488" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B488" s="7"/>
+      <c r="I488" s="7"/>
+    </row>
+    <row r="489" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B489" s="7"/>
+      <c r="I489" s="7"/>
+    </row>
+    <row r="490" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B490" s="7"/>
+      <c r="I490" s="7"/>
+    </row>
+    <row r="491" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B491" s="7"/>
+      <c r="I491" s="7"/>
+    </row>
+    <row r="492" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B492" s="7"/>
+      <c r="I492" s="7"/>
+    </row>
+    <row r="493" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B493" s="7"/>
+      <c r="I493" s="7"/>
+    </row>
+    <row r="494" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B494" s="7"/>
+      <c r="I494" s="7"/>
+    </row>
+    <row r="495" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B495" s="7"/>
+      <c r="I495" s="7"/>
+    </row>
+    <row r="496" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B496" s="7"/>
+      <c r="I496" s="7"/>
+    </row>
+    <row r="497" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B497" s="7"/>
+      <c r="I497" s="7"/>
+    </row>
+    <row r="498" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B498" s="7"/>
+      <c r="I498" s="7"/>
+    </row>
+    <row r="499" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B499" s="7"/>
+      <c r="I499" s="7"/>
+    </row>
+    <row r="500" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B500" s="7"/>
+      <c r="I500" s="7"/>
+    </row>
+    <row r="501" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B501" s="7"/>
+      <c r="I501" s="7"/>
+    </row>
+    <row r="502" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B502" s="7"/>
+      <c r="I502" s="7"/>
+    </row>
+    <row r="503" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B503" s="7"/>
+      <c r="I503" s="7"/>
+    </row>
+    <row r="504" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B504" s="7"/>
+      <c r="I504" s="7"/>
+    </row>
+    <row r="505" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B505" s="7"/>
+      <c r="I505" s="7"/>
+    </row>
+    <row r="506" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B506" s="7"/>
+      <c r="I506" s="7"/>
+    </row>
+    <row r="507" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B507" s="7"/>
+      <c r="I507" s="7"/>
+    </row>
+    <row r="508" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B508" s="7"/>
+      <c r="I508" s="7"/>
+    </row>
+    <row r="509" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B509" s="7"/>
+      <c r="I509" s="7"/>
+    </row>
+    <row r="510" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B510" s="7"/>
+      <c r="I510" s="7"/>
+    </row>
+    <row r="511" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B511" s="7"/>
+      <c r="I511" s="7"/>
+    </row>
+    <row r="512" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B512" s="7"/>
+      <c r="I512" s="7"/>
+    </row>
+    <row r="513" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B513" s="7"/>
+      <c r="I513" s="7"/>
+    </row>
+    <row r="514" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B514" s="7"/>
+      <c r="I514" s="7"/>
+    </row>
+    <row r="515" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B515" s="7"/>
+      <c r="I515" s="7"/>
+    </row>
+    <row r="516" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B516" s="7"/>
+      <c r="I516" s="7"/>
+    </row>
+    <row r="517" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B517" s="7"/>
+      <c r="I517" s="7"/>
+    </row>
+    <row r="518" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B518" s="7"/>
+      <c r="I518" s="7"/>
+    </row>
+    <row r="519" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B519" s="7"/>
+      <c r="I519" s="7"/>
+    </row>
+    <row r="520" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B520" s="7"/>
+      <c r="I520" s="7"/>
+    </row>
+    <row r="521" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B521" s="7"/>
+      <c r="I521" s="7"/>
+    </row>
+    <row r="522" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B522" s="7"/>
+      <c r="I522" s="7"/>
+    </row>
+    <row r="523" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B523" s="7"/>
+      <c r="I523" s="7"/>
+    </row>
+    <row r="524" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B524" s="7"/>
+      <c r="I524" s="7"/>
+    </row>
+    <row r="525" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B525" s="7"/>
+      <c r="I525" s="7"/>
+    </row>
+    <row r="526" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B526" s="7"/>
+      <c r="I526" s="7"/>
+    </row>
+    <row r="527" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B527" s="7"/>
+      <c r="I527" s="7"/>
+    </row>
+    <row r="528" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B528" s="7"/>
+      <c r="I528" s="7"/>
+    </row>
+    <row r="529" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B529" s="7"/>
+      <c r="I529" s="7"/>
+    </row>
+    <row r="530" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B530" s="7"/>
+      <c r="I530" s="7"/>
+    </row>
+    <row r="531" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B531" s="7"/>
+      <c r="I531" s="7"/>
+    </row>
+    <row r="532" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B532" s="7"/>
+      <c r="I532" s="7"/>
+    </row>
+    <row r="533" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B533" s="7"/>
+      <c r="I533" s="7"/>
+    </row>
+    <row r="534" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B534" s="7"/>
+      <c r="I534" s="7"/>
+    </row>
+    <row r="535" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B535" s="7"/>
+      <c r="I535" s="7"/>
+    </row>
+    <row r="536" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B536" s="7"/>
+      <c r="I536" s="7"/>
+    </row>
+    <row r="537" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B537" s="7"/>
+      <c r="I537" s="7"/>
+    </row>
+    <row r="538" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B538" s="7"/>
+      <c r="I538" s="7"/>
+    </row>
+    <row r="539" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B539" s="7"/>
+      <c r="I539" s="7"/>
+    </row>
+    <row r="540" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B540" s="7"/>
+      <c r="I540" s="7"/>
+    </row>
+    <row r="541" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B541" s="7"/>
+      <c r="I541" s="7"/>
+    </row>
+    <row r="542" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B542" s="7"/>
+      <c r="I542" s="7"/>
+    </row>
+    <row r="543" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B543" s="7"/>
+      <c r="I543" s="7"/>
+    </row>
+    <row r="544" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B544" s="7"/>
+      <c r="I544" s="7"/>
+    </row>
+    <row r="545" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B545" s="7"/>
+      <c r="I545" s="7"/>
+    </row>
+    <row r="546" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B546" s="7"/>
+      <c r="I546" s="7"/>
+    </row>
+    <row r="547" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B547" s="7"/>
+      <c r="I547" s="7"/>
+    </row>
+    <row r="548" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B548" s="7"/>
+      <c r="I548" s="7"/>
+    </row>
+    <row r="549" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B549" s="7"/>
+      <c r="I549" s="7"/>
+    </row>
+    <row r="550" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B550" s="7"/>
+      <c r="I550" s="7"/>
+    </row>
+    <row r="551" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B551" s="7"/>
+      <c r="I551" s="7"/>
+    </row>
+    <row r="552" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B552" s="7"/>
+      <c r="I552" s="7"/>
+    </row>
+    <row r="553" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B553" s="7"/>
+      <c r="I553" s="7"/>
+    </row>
+    <row r="554" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B554" s="7"/>
+      <c r="I554" s="7"/>
+    </row>
+    <row r="555" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B555" s="7"/>
+      <c r="I555" s="7"/>
+    </row>
+    <row r="556" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B556" s="7"/>
+      <c r="I556" s="7"/>
+    </row>
+    <row r="557" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B557" s="7"/>
+      <c r="I557" s="7"/>
+    </row>
+    <row r="558" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B558" s="7"/>
+      <c r="I558" s="7"/>
+    </row>
+    <row r="559" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B559" s="7"/>
+      <c r="I559" s="7"/>
+    </row>
+    <row r="560" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B560" s="7"/>
+      <c r="I560" s="7"/>
+    </row>
+    <row r="561" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B561" s="7"/>
+      <c r="I561" s="7"/>
+    </row>
+    <row r="562" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B562" s="7"/>
+      <c r="I562" s="7"/>
+    </row>
+    <row r="563" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B563" s="7"/>
+      <c r="I563" s="7"/>
+    </row>
+    <row r="564" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B564" s="7"/>
+      <c r="I564" s="7"/>
+    </row>
+    <row r="565" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B565" s="7"/>
+      <c r="I565" s="7"/>
+    </row>
+    <row r="566" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B566" s="7"/>
+      <c r="I566" s="7"/>
+    </row>
+    <row r="567" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B567" s="7"/>
+      <c r="I567" s="7"/>
+    </row>
+    <row r="568" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B568" s="7"/>
+      <c r="I568" s="7"/>
+    </row>
+    <row r="569" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B569" s="7"/>
+      <c r="I569" s="7"/>
+    </row>
+    <row r="570" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B570" s="7"/>
+      <c r="I570" s="7"/>
+    </row>
+    <row r="571" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B571" s="7"/>
+      <c r="I571" s="7"/>
+    </row>
+    <row r="572" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B572" s="7"/>
+      <c r="I572" s="7"/>
+    </row>
+    <row r="573" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B573" s="7"/>
+      <c r="I573" s="7"/>
+    </row>
+    <row r="574" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B574" s="7"/>
+      <c r="I574" s="7"/>
+    </row>
+    <row r="575" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B575" s="7"/>
+      <c r="I575" s="7"/>
+    </row>
+    <row r="576" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B576" s="7"/>
+      <c r="I576" s="7"/>
+    </row>
+    <row r="577" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B577" s="7"/>
+      <c r="I577" s="7"/>
+    </row>
+    <row r="578" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B578" s="7"/>
+      <c r="I578" s="7"/>
+    </row>
+    <row r="579" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B579" s="7"/>
+      <c r="I579" s="7"/>
+    </row>
+    <row r="580" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B580" s="7"/>
+      <c r="I580" s="7"/>
+    </row>
+    <row r="581" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B581" s="7"/>
+      <c r="I581" s="7"/>
+    </row>
+    <row r="582" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B582" s="7"/>
+      <c r="I582" s="7"/>
+    </row>
+    <row r="583" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B583" s="7"/>
+      <c r="I583" s="7"/>
+    </row>
+    <row r="584" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B584" s="7"/>
+      <c r="I584" s="7"/>
+    </row>
+    <row r="585" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B585" s="7"/>
+      <c r="I585" s="7"/>
+    </row>
+    <row r="586" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B586" s="7"/>
+      <c r="I586" s="7"/>
+    </row>
+    <row r="587" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B587" s="7"/>
+      <c r="I587" s="7"/>
+    </row>
+    <row r="588" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B588" s="7"/>
+      <c r="I588" s="7"/>
+    </row>
+    <row r="589" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B589" s="7"/>
+      <c r="I589" s="7"/>
+    </row>
+    <row r="590" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B590" s="7"/>
+      <c r="I590" s="7"/>
+    </row>
+    <row r="591" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B591" s="7"/>
+      <c r="I591" s="7"/>
+    </row>
+    <row r="592" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B592" s="7"/>
+      <c r="I592" s="7"/>
+    </row>
+    <row r="593" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B593" s="7"/>
+      <c r="I593" s="7"/>
+    </row>
+    <row r="594" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B594" s="7"/>
+      <c r="I594" s="7"/>
+    </row>
+    <row r="595" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B595" s="7"/>
+      <c r="I595" s="7"/>
+    </row>
+    <row r="596" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B596" s="7"/>
+      <c r="I596" s="7"/>
+    </row>
+    <row r="597" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B597" s="7"/>
+      <c r="I597" s="7"/>
+    </row>
+    <row r="598" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B598" s="7"/>
+      <c r="I598" s="7"/>
+    </row>
+    <row r="599" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B599" s="7"/>
+      <c r="I599" s="7"/>
+    </row>
+    <row r="600" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B600" s="7"/>
+      <c r="I600" s="7"/>
+    </row>
+    <row r="601" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B601" s="7"/>
+      <c r="I601" s="7"/>
+    </row>
+    <row r="602" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B602" s="7"/>
+      <c r="I602" s="7"/>
+    </row>
+    <row r="603" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B603" s="7"/>
+      <c r="I603" s="7"/>
+    </row>
+    <row r="604" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B604" s="7"/>
+      <c r="I604" s="7"/>
+    </row>
+    <row r="605" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B605" s="7"/>
+      <c r="I605" s="7"/>
+    </row>
+    <row r="606" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B606" s="7"/>
+      <c r="I606" s="7"/>
+    </row>
+    <row r="607" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B607" s="7"/>
+      <c r="I607" s="7"/>
+    </row>
+    <row r="608" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B608" s="7"/>
+      <c r="I608" s="7"/>
+    </row>
+    <row r="609" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B609" s="7"/>
+      <c r="I609" s="7"/>
+    </row>
+    <row r="610" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B610" s="7"/>
+      <c r="I610" s="7"/>
+    </row>
+    <row r="611" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B611" s="7"/>
+      <c r="I611" s="7"/>
+    </row>
+    <row r="612" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B612" s="7"/>
+      <c r="I612" s="7"/>
+    </row>
+    <row r="613" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B613" s="7"/>
+      <c r="I613" s="7"/>
+    </row>
+    <row r="614" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B614" s="7"/>
+      <c r="I614" s="7"/>
+    </row>
+    <row r="615" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B615" s="7"/>
+      <c r="I615" s="7"/>
+    </row>
+    <row r="616" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B616" s="7"/>
+      <c r="I616" s="7"/>
+    </row>
+    <row r="617" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B617" s="7"/>
+      <c r="I617" s="7"/>
+    </row>
+    <row r="618" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B618" s="7"/>
+      <c r="I618" s="7"/>
+    </row>
+    <row r="619" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B619" s="7"/>
+      <c r="I619" s="7"/>
+    </row>
+    <row r="620" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B620" s="7"/>
+      <c r="I620" s="7"/>
+    </row>
+    <row r="621" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B621" s="7"/>
+      <c r="I621" s="7"/>
+    </row>
+    <row r="622" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B622" s="7"/>
+      <c r="I622" s="7"/>
+    </row>
+    <row r="623" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B623" s="7"/>
+      <c r="I623" s="7"/>
+    </row>
+    <row r="624" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B624" s="7"/>
+      <c r="I624" s="7"/>
+    </row>
+    <row r="625" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B625" s="7"/>
+      <c r="I625" s="7"/>
+    </row>
+    <row r="626" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B626" s="7"/>
+      <c r="I626" s="7"/>
+    </row>
+    <row r="627" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B627" s="7"/>
+      <c r="I627" s="7"/>
+    </row>
+    <row r="628" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B628" s="7"/>
+      <c r="I628" s="7"/>
+    </row>
+    <row r="629" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B629" s="7"/>
+      <c r="I629" s="7"/>
+    </row>
+    <row r="630" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B630" s="7"/>
+      <c r="I630" s="7"/>
+    </row>
+    <row r="631" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B631" s="7"/>
+      <c r="I631" s="7"/>
+    </row>
+    <row r="632" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B632" s="7"/>
+      <c r="I632" s="7"/>
+    </row>
+    <row r="633" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B633" s="7"/>
+      <c r="I633" s="7"/>
+    </row>
+    <row r="634" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B634" s="7"/>
+      <c r="I634" s="7"/>
+    </row>
+    <row r="635" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B635" s="7"/>
+      <c r="I635" s="7"/>
+    </row>
+    <row r="636" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B636" s="7"/>
+      <c r="I636" s="7"/>
+    </row>
+    <row r="637" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B637" s="7"/>
+      <c r="I637" s="7"/>
+    </row>
+    <row r="638" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B638" s="7"/>
+      <c r="I638" s="7"/>
+    </row>
+    <row r="639" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B639" s="7"/>
+      <c r="I639" s="7"/>
+    </row>
+    <row r="640" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B640" s="7"/>
+      <c r="I640" s="7"/>
+    </row>
+    <row r="641" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B641" s="7"/>
+      <c r="I641" s="7"/>
+    </row>
+    <row r="642" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B642" s="7"/>
+      <c r="I642" s="7"/>
+    </row>
+    <row r="643" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B643" s="7"/>
+      <c r="I643" s="7"/>
+    </row>
+    <row r="644" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B644" s="7"/>
+      <c r="I644" s="7"/>
+    </row>
+    <row r="645" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B645" s="7"/>
+      <c r="I645" s="7"/>
+    </row>
+    <row r="646" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B646" s="7"/>
+      <c r="I646" s="7"/>
+    </row>
+    <row r="647" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B647" s="7"/>
+      <c r="I647" s="7"/>
+    </row>
+    <row r="648" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B648" s="7"/>
+      <c r="I648" s="7"/>
+    </row>
+    <row r="649" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B649" s="7"/>
+      <c r="I649" s="7"/>
+    </row>
+    <row r="650" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B650" s="7"/>
+      <c r="I650" s="7"/>
+    </row>
+    <row r="651" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B651" s="7"/>
+      <c r="I651" s="7"/>
+    </row>
+    <row r="652" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B652" s="7"/>
+      <c r="I652" s="7"/>
+    </row>
+    <row r="653" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B653" s="7"/>
+      <c r="I653" s="7"/>
+    </row>
+    <row r="654" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B654" s="7"/>
+      <c r="I654" s="7"/>
+    </row>
+    <row r="655" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B655" s="7"/>
+      <c r="I655" s="7"/>
+    </row>
+    <row r="656" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B656" s="7"/>
+      <c r="I656" s="7"/>
+    </row>
+    <row r="657" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B657" s="7"/>
+      <c r="I657" s="7"/>
+    </row>
+    <row r="658" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B658" s="7"/>
+      <c r="I658" s="7"/>
+    </row>
+    <row r="659" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B659" s="7"/>
+      <c r="I659" s="7"/>
+    </row>
+    <row r="660" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B660" s="7"/>
+      <c r="I660" s="7"/>
+    </row>
+    <row r="661" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B661" s="7"/>
+      <c r="I661" s="7"/>
+    </row>
+    <row r="662" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B662" s="7"/>
+      <c r="I662" s="7"/>
+    </row>
+    <row r="663" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B663" s="7"/>
+      <c r="I663" s="7"/>
+    </row>
+    <row r="664" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B664" s="7"/>
+      <c r="I664" s="7"/>
+    </row>
+    <row r="665" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B665" s="7"/>
+      <c r="I665" s="7"/>
+    </row>
+    <row r="666" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B666" s="7"/>
+      <c r="I666" s="7"/>
+    </row>
+    <row r="667" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B667" s="7"/>
+      <c r="I667" s="7"/>
+    </row>
+    <row r="668" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B668" s="7"/>
+      <c r="I668" s="7"/>
+    </row>
+    <row r="669" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B669" s="7"/>
+      <c r="I669" s="7"/>
+    </row>
+    <row r="670" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B670" s="7"/>
+      <c r="I670" s="7"/>
+    </row>
+    <row r="671" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B671" s="7"/>
+      <c r="I671" s="7"/>
+    </row>
+    <row r="672" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B672" s="7"/>
+      <c r="I672" s="7"/>
+    </row>
+    <row r="673" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B673" s="7"/>
+      <c r="I673" s="7"/>
+    </row>
+    <row r="674" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B674" s="7"/>
+      <c r="I674" s="7"/>
+    </row>
+    <row r="675" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B675" s="7"/>
+      <c r="I675" s="7"/>
+    </row>
+    <row r="676" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B676" s="7"/>
+      <c r="I676" s="7"/>
+    </row>
+    <row r="677" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B677" s="7"/>
+      <c r="I677" s="7"/>
+    </row>
+    <row r="678" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B678" s="7"/>
+      <c r="I678" s="7"/>
+    </row>
+    <row r="679" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B679" s="7"/>
+      <c r="I679" s="7"/>
+    </row>
+    <row r="680" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B680" s="7"/>
+      <c r="I680" s="7"/>
+    </row>
+    <row r="681" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B681" s="7"/>
+      <c r="I681" s="7"/>
+    </row>
+    <row r="682" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B682" s="7"/>
+      <c r="I682" s="7"/>
+    </row>
+    <row r="683" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B683" s="7"/>
+      <c r="I683" s="7"/>
+    </row>
+    <row r="684" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B684" s="7"/>
+      <c r="I684" s="7"/>
+    </row>
+    <row r="685" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B685" s="7"/>
+      <c r="I685" s="7"/>
+    </row>
+    <row r="686" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B686" s="7"/>
+      <c r="I686" s="7"/>
+    </row>
+    <row r="687" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B687" s="7"/>
+      <c r="I687" s="7"/>
+    </row>
+    <row r="688" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B688" s="7"/>
+      <c r="I688" s="7"/>
+    </row>
+    <row r="689" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B689" s="7"/>
+      <c r="I689" s="7"/>
+    </row>
+    <row r="690" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B690" s="7"/>
+      <c r="I690" s="7"/>
+    </row>
+    <row r="691" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B691" s="7"/>
+      <c r="I691" s="7"/>
+    </row>
+    <row r="692" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B692" s="7"/>
+      <c r="I692" s="7"/>
+    </row>
+    <row r="693" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B693" s="7"/>
+      <c r="I693" s="7"/>
+    </row>
+    <row r="694" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B694" s="7"/>
+      <c r="I694" s="7"/>
+    </row>
+    <row r="695" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B695" s="7"/>
+      <c r="I695" s="7"/>
+    </row>
+    <row r="696" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B696" s="7"/>
+      <c r="I696" s="7"/>
+    </row>
+    <row r="697" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B697" s="7"/>
+      <c r="I697" s="7"/>
+    </row>
+    <row r="698" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B698" s="7"/>
+      <c r="I698" s="7"/>
+    </row>
+    <row r="699" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B699" s="7"/>
+      <c r="I699" s="7"/>
+    </row>
+    <row r="700" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B700" s="7"/>
+      <c r="I700" s="7"/>
+    </row>
+    <row r="701" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B701" s="7"/>
+      <c r="I701" s="7"/>
+    </row>
+    <row r="702" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B702" s="7"/>
+      <c r="I702" s="7"/>
+    </row>
+    <row r="703" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B703" s="7"/>
+      <c r="I703" s="7"/>
+    </row>
+    <row r="704" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B704" s="7"/>
+      <c r="I704" s="7"/>
+    </row>
+    <row r="705" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B705" s="7"/>
+      <c r="I705" s="7"/>
+    </row>
+    <row r="706" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B706" s="7"/>
+      <c r="I706" s="7"/>
+    </row>
+    <row r="707" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B707" s="7"/>
+      <c r="I707" s="7"/>
+    </row>
+    <row r="708" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B708" s="7"/>
+      <c r="I708" s="7"/>
+    </row>
+    <row r="709" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B709" s="7"/>
+      <c r="I709" s="7"/>
+    </row>
+    <row r="710" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B710" s="7"/>
+      <c r="I710" s="7"/>
+    </row>
+    <row r="711" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B711" s="7"/>
+      <c r="I711" s="7"/>
+    </row>
+    <row r="712" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B712" s="7"/>
+      <c r="I712" s="7"/>
+    </row>
+    <row r="713" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B713" s="7"/>
+      <c r="I713" s="7"/>
+    </row>
+    <row r="714" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B714" s="7"/>
+      <c r="I714" s="7"/>
+    </row>
+    <row r="715" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B715" s="7"/>
+      <c r="I715" s="7"/>
+    </row>
+    <row r="716" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B716" s="7"/>
+      <c r="I716" s="7"/>
+    </row>
+    <row r="717" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B717" s="7"/>
+      <c r="I717" s="7"/>
+    </row>
+    <row r="718" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B718" s="7"/>
+      <c r="I718" s="7"/>
+    </row>
+    <row r="719" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B719" s="7"/>
+      <c r="I719" s="7"/>
+    </row>
+    <row r="720" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B720" s="7"/>
+      <c r="I720" s="7"/>
+    </row>
+    <row r="721" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B721" s="7"/>
+      <c r="I721" s="7"/>
+    </row>
+    <row r="722" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B722" s="7"/>
+      <c r="I722" s="7"/>
+    </row>
+    <row r="723" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B723" s="7"/>
+      <c r="I723" s="7"/>
+    </row>
+    <row r="724" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B724" s="7"/>
+      <c r="I724" s="7"/>
+    </row>
+    <row r="725" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B725" s="7"/>
+      <c r="I725" s="7"/>
+    </row>
+    <row r="726" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B726" s="7"/>
+      <c r="I726" s="7"/>
+    </row>
+    <row r="727" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B727" s="7"/>
+      <c r="I727" s="7"/>
+    </row>
+    <row r="728" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B728" s="7"/>
+      <c r="I728" s="7"/>
+    </row>
+    <row r="729" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B729" s="7"/>
+      <c r="I729" s="7"/>
+    </row>
+    <row r="730" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B730" s="7"/>
+      <c r="I730" s="7"/>
+    </row>
+    <row r="731" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B731" s="7"/>
+      <c r="I731" s="7"/>
+    </row>
+    <row r="732" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B732" s="7"/>
+      <c r="I732" s="7"/>
+    </row>
+    <row r="733" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B733" s="7"/>
+      <c r="I733" s="7"/>
+    </row>
+    <row r="734" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B734" s="7"/>
+      <c r="I734" s="7"/>
+    </row>
+    <row r="735" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B735" s="7"/>
+      <c r="I735" s="7"/>
+    </row>
+    <row r="736" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B736" s="7"/>
+      <c r="I736" s="7"/>
+    </row>
+    <row r="737" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B737" s="7"/>
+      <c r="I737" s="7"/>
+    </row>
+    <row r="738" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B738" s="7"/>
+      <c r="I738" s="7"/>
+    </row>
+    <row r="739" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B739" s="7"/>
+      <c r="I739" s="7"/>
+    </row>
+    <row r="740" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B740" s="7"/>
+      <c r="I740" s="7"/>
+    </row>
+    <row r="741" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B741" s="7"/>
+      <c r="I741" s="7"/>
+    </row>
+    <row r="742" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B742" s="7"/>
+      <c r="I742" s="7"/>
+    </row>
+    <row r="743" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B743" s="7"/>
+      <c r="I743" s="7"/>
+    </row>
+    <row r="744" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B744" s="7"/>
+      <c r="I744" s="7"/>
+    </row>
+    <row r="745" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B745" s="7"/>
+      <c r="I745" s="7"/>
+    </row>
+    <row r="746" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B746" s="7"/>
+      <c r="I746" s="7"/>
+    </row>
+    <row r="747" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B747" s="7"/>
+      <c r="I747" s="7"/>
+    </row>
+    <row r="748" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B748" s="7"/>
+      <c r="I748" s="7"/>
+    </row>
+    <row r="749" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B749" s="7"/>
+      <c r="I749" s="7"/>
+    </row>
+    <row r="750" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B750" s="7"/>
+      <c r="I750" s="7"/>
+    </row>
+    <row r="751" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B751" s="7"/>
+      <c r="I751" s="7"/>
+    </row>
+    <row r="752" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B752" s="7"/>
+      <c r="I752" s="7"/>
+    </row>
+    <row r="753" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B753" s="7"/>
+      <c r="I753" s="7"/>
+    </row>
+    <row r="754" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B754" s="7"/>
+      <c r="I754" s="7"/>
+    </row>
+    <row r="755" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B755" s="7"/>
+      <c r="I755" s="7"/>
+    </row>
+    <row r="756" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B756" s="7"/>
+      <c r="I756" s="7"/>
+    </row>
+    <row r="757" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B757" s="7"/>
+      <c r="I757" s="7"/>
+    </row>
+    <row r="758" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B758" s="7"/>
+      <c r="I758" s="7"/>
+    </row>
+    <row r="759" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B759" s="7"/>
+      <c r="I759" s="7"/>
+    </row>
+    <row r="760" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B760" s="7"/>
+      <c r="I760" s="7"/>
+    </row>
+    <row r="761" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B761" s="7"/>
+      <c r="I761" s="7"/>
+    </row>
+    <row r="762" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B762" s="7"/>
+      <c r="I762" s="7"/>
+    </row>
+    <row r="763" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B763" s="7"/>
+      <c r="I763" s="7"/>
+    </row>
+    <row r="764" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B764" s="7"/>
+      <c r="I764" s="7"/>
+    </row>
+    <row r="765" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B765" s="7"/>
+      <c r="I765" s="7"/>
+    </row>
+    <row r="766" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B766" s="7"/>
+      <c r="I766" s="7"/>
+    </row>
+    <row r="767" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B767" s="7"/>
+      <c r="I767" s="7"/>
+    </row>
+    <row r="768" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B768" s="7"/>
+      <c r="I768" s="7"/>
+    </row>
+    <row r="769" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B769" s="7"/>
+      <c r="I769" s="7"/>
+    </row>
+    <row r="770" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B770" s="7"/>
+      <c r="I770" s="7"/>
+    </row>
+    <row r="771" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B771" s="7"/>
+      <c r="I771" s="7"/>
+    </row>
+    <row r="772" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B772" s="7"/>
+      <c r="I772" s="7"/>
+    </row>
+    <row r="773" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B773" s="7"/>
+      <c r="I773" s="7"/>
+    </row>
+    <row r="774" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B774" s="7"/>
+      <c r="I774" s="7"/>
+    </row>
+    <row r="775" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B775" s="7"/>
+      <c r="I775" s="7"/>
+    </row>
+    <row r="776" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B776" s="7"/>
+      <c r="I776" s="7"/>
+    </row>
+    <row r="777" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B777" s="7"/>
+      <c r="I777" s="7"/>
+    </row>
+    <row r="778" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B778" s="7"/>
+      <c r="I778" s="7"/>
+    </row>
+    <row r="779" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B779" s="7"/>
+      <c r="I779" s="7"/>
+    </row>
+    <row r="780" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B780" s="7"/>
+      <c r="I780" s="7"/>
+    </row>
+    <row r="781" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B781" s="7"/>
+      <c r="I781" s="7"/>
+    </row>
+    <row r="782" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B782" s="7"/>
+      <c r="I782" s="7"/>
+    </row>
+    <row r="783" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B783" s="7"/>
+      <c r="I783" s="7"/>
+    </row>
+    <row r="784" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B784" s="7"/>
+      <c r="I784" s="7"/>
+    </row>
+    <row r="785" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B785" s="7"/>
+      <c r="I785" s="7"/>
+    </row>
+    <row r="786" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B786" s="7"/>
+      <c r="I786" s="7"/>
+    </row>
+    <row r="787" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B787" s="7"/>
+      <c r="I787" s="7"/>
+    </row>
+    <row r="788" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B788" s="7"/>
+      <c r="I788" s="7"/>
+    </row>
+    <row r="789" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B789" s="7"/>
+      <c r="I789" s="7"/>
+    </row>
+    <row r="790" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B790" s="7"/>
+      <c r="I790" s="7"/>
+    </row>
+    <row r="791" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B791" s="7"/>
+      <c r="I791" s="7"/>
+    </row>
+    <row r="792" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B792" s="7"/>
+      <c r="I792" s="7"/>
+    </row>
+    <row r="793" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B793" s="7"/>
+      <c r="I793" s="7"/>
+    </row>
+    <row r="794" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B794" s="7"/>
+      <c r="I794" s="7"/>
+    </row>
+    <row r="795" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B795" s="7"/>
+      <c r="I795" s="7"/>
+    </row>
+    <row r="796" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B796" s="7"/>
+      <c r="I796" s="7"/>
+    </row>
+    <row r="797" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B797" s="7"/>
+      <c r="I797" s="7"/>
+    </row>
+    <row r="798" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B798" s="7"/>
+      <c r="I798" s="7"/>
+    </row>
+    <row r="799" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B799" s="7"/>
+      <c r="I799" s="7"/>
+    </row>
+    <row r="800" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B800" s="7"/>
+      <c r="I800" s="7"/>
+    </row>
+    <row r="801" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B801" s="7"/>
+      <c r="I801" s="7"/>
+    </row>
+    <row r="802" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B802" s="7"/>
+      <c r="I802" s="7"/>
+    </row>
+    <row r="803" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B803" s="7"/>
+      <c r="I803" s="7"/>
+    </row>
+    <row r="804" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B804" s="7"/>
+      <c r="I804" s="7"/>
+    </row>
+    <row r="805" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B805" s="7"/>
+      <c r="I805" s="7"/>
+    </row>
+    <row r="806" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B806" s="7"/>
+      <c r="I806" s="7"/>
+    </row>
+    <row r="807" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B807" s="7"/>
+      <c r="I807" s="7"/>
+    </row>
+    <row r="808" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B808" s="7"/>
+      <c r="I808" s="7"/>
+    </row>
+    <row r="809" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B809" s="7"/>
+      <c r="I809" s="7"/>
+    </row>
+    <row r="810" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B810" s="7"/>
+      <c r="I810" s="7"/>
+    </row>
+    <row r="811" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B811" s="7"/>
+      <c r="I811" s="7"/>
+    </row>
+    <row r="812" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B812" s="7"/>
+      <c r="I812" s="7"/>
+    </row>
+    <row r="813" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B813" s="7"/>
+      <c r="I813" s="7"/>
+    </row>
+    <row r="814" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B814" s="7"/>
+      <c r="I814" s="7"/>
+    </row>
+    <row r="815" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B815" s="7"/>
+      <c r="I815" s="7"/>
+    </row>
+    <row r="816" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B816" s="7"/>
+      <c r="I816" s="7"/>
+    </row>
+    <row r="817" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B817" s="7"/>
+      <c r="I817" s="7"/>
+    </row>
+    <row r="818" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B818" s="7"/>
+      <c r="I818" s="7"/>
+    </row>
+    <row r="819" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B819" s="7"/>
+      <c r="I819" s="7"/>
+    </row>
+    <row r="820" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B820" s="7"/>
+      <c r="I820" s="7"/>
+    </row>
+    <row r="821" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B821" s="7"/>
+      <c r="I821" s="7"/>
+    </row>
+    <row r="822" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B822" s="7"/>
+      <c r="I822" s="7"/>
+    </row>
+    <row r="823" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B823" s="7"/>
+      <c r="I823" s="7"/>
+    </row>
+    <row r="824" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B824" s="7"/>
+      <c r="I824" s="7"/>
+    </row>
+    <row r="825" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B825" s="7"/>
+      <c r="I825" s="7"/>
+    </row>
+    <row r="826" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B826" s="7"/>
+      <c r="I826" s="7"/>
+    </row>
+    <row r="827" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B827" s="7"/>
+      <c r="I827" s="7"/>
+    </row>
+    <row r="828" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B828" s="7"/>
+      <c r="I828" s="7"/>
+    </row>
+    <row r="829" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B829" s="7"/>
+      <c r="I829" s="7"/>
+    </row>
+    <row r="830" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B830" s="7"/>
+      <c r="I830" s="7"/>
+    </row>
+    <row r="831" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B831" s="7"/>
+      <c r="I831" s="7"/>
+    </row>
+    <row r="832" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B832" s="7"/>
+      <c r="I832" s="7"/>
+    </row>
+    <row r="833" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B833" s="7"/>
+      <c r="I833" s="7"/>
+    </row>
+    <row r="834" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B834" s="7"/>
+      <c r="I834" s="7"/>
+    </row>
+    <row r="835" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B835" s="7"/>
+      <c r="I835" s="7"/>
+    </row>
+    <row r="836" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B836" s="7"/>
+      <c r="I836" s="7"/>
+    </row>
+    <row r="837" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B837" s="7"/>
+      <c r="I837" s="7"/>
+    </row>
+    <row r="838" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B838" s="7"/>
+      <c r="I838" s="7"/>
+    </row>
+    <row r="839" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B839" s="7"/>
+      <c r="I839" s="7"/>
+    </row>
+    <row r="840" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B840" s="7"/>
+      <c r="I840" s="7"/>
+    </row>
+    <row r="841" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B841" s="7"/>
+      <c r="I841" s="7"/>
+    </row>
+    <row r="842" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B842" s="7"/>
+      <c r="I842" s="7"/>
+    </row>
+    <row r="843" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B843" s="7"/>
+      <c r="I843" s="7"/>
+    </row>
+    <row r="844" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B844" s="7"/>
+      <c r="I844" s="7"/>
+    </row>
+    <row r="845" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B845" s="7"/>
+      <c r="I845" s="7"/>
+    </row>
+    <row r="846" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B846" s="7"/>
+      <c r="I846" s="7"/>
+    </row>
+    <row r="847" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B847" s="7"/>
+      <c r="I847" s="7"/>
+    </row>
+    <row r="848" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B848" s="7"/>
+      <c r="I848" s="7"/>
+    </row>
+    <row r="849" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B849" s="7"/>
+      <c r="I849" s="7"/>
+    </row>
+    <row r="850" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B850" s="7"/>
+      <c r="I850" s="7"/>
+    </row>
+    <row r="851" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B851" s="7"/>
+      <c r="I851" s="7"/>
+    </row>
+    <row r="852" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B852" s="7"/>
+      <c r="I852" s="7"/>
+    </row>
+    <row r="853" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B853" s="7"/>
+      <c r="I853" s="7"/>
+    </row>
+    <row r="854" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B854" s="7"/>
+      <c r="I854" s="7"/>
+    </row>
+    <row r="855" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B855" s="7"/>
+      <c r="I855" s="7"/>
+    </row>
+    <row r="856" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B856" s="7"/>
+      <c r="I856" s="7"/>
+    </row>
+    <row r="857" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B857" s="7"/>
+      <c r="I857" s="7"/>
+    </row>
+    <row r="858" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B858" s="7"/>
+      <c r="I858" s="7"/>
+    </row>
+    <row r="859" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B859" s="7"/>
+      <c r="I859" s="7"/>
+    </row>
+    <row r="860" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B860" s="7"/>
+      <c r="I860" s="7"/>
+    </row>
+    <row r="861" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B861" s="7"/>
+      <c r="I861" s="7"/>
+    </row>
+    <row r="862" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B862" s="7"/>
+      <c r="I862" s="7"/>
+    </row>
+    <row r="863" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B863" s="7"/>
+      <c r="I863" s="7"/>
+    </row>
+    <row r="864" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B864" s="7"/>
+      <c r="I864" s="7"/>
+    </row>
+    <row r="865" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B865" s="7"/>
+      <c r="I865" s="7"/>
+    </row>
+    <row r="866" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B866" s="7"/>
+      <c r="I866" s="7"/>
+    </row>
+    <row r="867" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B867" s="7"/>
+      <c r="I867" s="7"/>
+    </row>
+    <row r="868" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B868" s="7"/>
+      <c r="I868" s="7"/>
+    </row>
+    <row r="869" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B869" s="7"/>
+      <c r="I869" s="7"/>
+    </row>
+    <row r="870" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B870" s="7"/>
+      <c r="I870" s="7"/>
+    </row>
+    <row r="871" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B871" s="7"/>
+      <c r="I871" s="7"/>
+    </row>
+    <row r="872" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B872" s="7"/>
+      <c r="I872" s="7"/>
+    </row>
+    <row r="873" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B873" s="7"/>
+      <c r="I873" s="7"/>
+    </row>
+    <row r="874" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B874" s="7"/>
+      <c r="I874" s="7"/>
+    </row>
+    <row r="875" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B875" s="7"/>
+      <c r="I875" s="7"/>
+    </row>
+    <row r="876" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B876" s="7"/>
+      <c r="I876" s="7"/>
+    </row>
+    <row r="877" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B877" s="7"/>
+      <c r="I877" s="7"/>
+    </row>
+    <row r="878" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B878" s="7"/>
+      <c r="I878" s="7"/>
+    </row>
+    <row r="879" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B879" s="7"/>
+      <c r="I879" s="7"/>
+    </row>
+    <row r="880" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B880" s="7"/>
+      <c r="I880" s="7"/>
+    </row>
+    <row r="881" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B881" s="7"/>
+      <c r="I881" s="7"/>
+    </row>
+    <row r="882" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B882" s="7"/>
+      <c r="I882" s="7"/>
+    </row>
+    <row r="883" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B883" s="7"/>
+      <c r="I883" s="7"/>
+    </row>
+    <row r="884" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B884" s="7"/>
+      <c r="I884" s="7"/>
+    </row>
+    <row r="885" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B885" s="7"/>
+      <c r="I885" s="7"/>
+    </row>
+    <row r="886" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B886" s="7"/>
+      <c r="I886" s="7"/>
+    </row>
+    <row r="887" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B887" s="7"/>
+      <c r="I887" s="7"/>
+    </row>
+    <row r="888" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B888" s="7"/>
+      <c r="I888" s="7"/>
+    </row>
+    <row r="889" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B889" s="7"/>
+      <c r="I889" s="7"/>
+    </row>
+    <row r="890" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B890" s="7"/>
+      <c r="I890" s="7"/>
+    </row>
+    <row r="891" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B891" s="7"/>
+      <c r="I891" s="7"/>
+    </row>
+    <row r="892" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B892" s="7"/>
+      <c r="I892" s="7"/>
+    </row>
+    <row r="893" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B893" s="7"/>
+      <c r="I893" s="7"/>
+    </row>
+    <row r="894" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B894" s="7"/>
+      <c r="I894" s="7"/>
+    </row>
+    <row r="895" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B895" s="7"/>
+      <c r="I895" s="7"/>
+    </row>
+    <row r="896" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B896" s="7"/>
+      <c r="I896" s="7"/>
+    </row>
+    <row r="897" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B897" s="7"/>
+      <c r="I897" s="7"/>
+    </row>
+    <row r="898" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B898" s="7"/>
+      <c r="I898" s="7"/>
+    </row>
+    <row r="899" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B899" s="7"/>
+      <c r="I899" s="7"/>
+    </row>
+    <row r="900" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B900" s="7"/>
+      <c r="I900" s="7"/>
+    </row>
+    <row r="901" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B901" s="7"/>
+      <c r="I901" s="7"/>
+    </row>
+    <row r="902" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B902" s="7"/>
+      <c r="I902" s="7"/>
+    </row>
+    <row r="903" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B903" s="7"/>
+      <c r="I903" s="7"/>
+    </row>
+    <row r="904" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B904" s="7"/>
+      <c r="I904" s="7"/>
+    </row>
+    <row r="905" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B905" s="7"/>
+      <c r="I905" s="7"/>
+    </row>
+    <row r="906" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B906" s="7"/>
+      <c r="I906" s="7"/>
+    </row>
+    <row r="907" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B907" s="7"/>
+      <c r="I907" s="7"/>
+    </row>
+    <row r="908" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B908" s="7"/>
+      <c r="I908" s="7"/>
+    </row>
+    <row r="909" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B909" s="7"/>
+      <c r="I909" s="7"/>
+    </row>
+    <row r="910" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B910" s="7"/>
+      <c r="I910" s="7"/>
+    </row>
+    <row r="911" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B911" s="7"/>
+      <c r="I911" s="7"/>
+    </row>
+    <row r="912" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B912" s="7"/>
+      <c r="I912" s="7"/>
+    </row>
+    <row r="913" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B913" s="7"/>
+      <c r="I913" s="7"/>
+    </row>
+    <row r="914" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B914" s="7"/>
+      <c r="I914" s="7"/>
+    </row>
+    <row r="915" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B915" s="7"/>
+      <c r="I915" s="7"/>
+    </row>
+    <row r="916" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B916" s="7"/>
+      <c r="I916" s="7"/>
+    </row>
+    <row r="917" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B917" s="7"/>
+      <c r="I917" s="7"/>
+    </row>
+    <row r="918" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B918" s="7"/>
+      <c r="I918" s="7"/>
+    </row>
+    <row r="919" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B919" s="7"/>
+      <c r="I919" s="7"/>
+    </row>
+    <row r="920" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B920" s="7"/>
+      <c r="I920" s="7"/>
+    </row>
+    <row r="921" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B921" s="7"/>
+      <c r="I921" s="7"/>
+    </row>
+    <row r="922" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B922" s="7"/>
+      <c r="I922" s="7"/>
+    </row>
+    <row r="923" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B923" s="7"/>
+      <c r="I923" s="7"/>
+    </row>
+    <row r="924" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B924" s="7"/>
+      <c r="I924" s="7"/>
+    </row>
+    <row r="925" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B925" s="7"/>
+      <c r="I925" s="7"/>
+    </row>
+    <row r="926" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B926" s="7"/>
+      <c r="I926" s="7"/>
+    </row>
+    <row r="927" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B927" s="7"/>
+      <c r="I927" s="7"/>
+    </row>
+    <row r="928" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B928" s="7"/>
+      <c r="I928" s="7"/>
+    </row>
+    <row r="929" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B929" s="7"/>
+      <c r="I929" s="7"/>
+    </row>
+    <row r="930" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B930" s="7"/>
+      <c r="I930" s="7"/>
+    </row>
+    <row r="931" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B931" s="7"/>
+      <c r="I931" s="7"/>
+    </row>
+    <row r="932" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B932" s="7"/>
+      <c r="I932" s="7"/>
+    </row>
+    <row r="933" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B933" s="7"/>
+      <c r="I933" s="7"/>
+    </row>
+    <row r="934" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B934" s="7"/>
+      <c r="I934" s="7"/>
+    </row>
+    <row r="935" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B935" s="7"/>
+      <c r="I935" s="7"/>
+    </row>
+    <row r="936" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B936" s="7"/>
+      <c r="I936" s="7"/>
+    </row>
+    <row r="937" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B937" s="7"/>
+      <c r="I937" s="7"/>
+    </row>
+    <row r="938" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B938" s="7"/>
+      <c r="I938" s="7"/>
+    </row>
+    <row r="939" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B939" s="7"/>
+      <c r="I939" s="7"/>
+    </row>
+    <row r="940" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B940" s="7"/>
+      <c r="I940" s="7"/>
+    </row>
+    <row r="941" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B941" s="7"/>
+      <c r="I941" s="7"/>
+    </row>
+    <row r="942" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B942" s="7"/>
+      <c r="I942" s="7"/>
+    </row>
+    <row r="943" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B943" s="7"/>
+      <c r="I943" s="7"/>
+    </row>
+    <row r="944" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B944" s="7"/>
+      <c r="I944" s="7"/>
+    </row>
+    <row r="945" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B945" s="7"/>
+      <c r="I945" s="7"/>
+    </row>
+    <row r="946" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B946" s="7"/>
+      <c r="I946" s="7"/>
+    </row>
+    <row r="947" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B947" s="7"/>
+      <c r="I947" s="7"/>
+    </row>
+    <row r="948" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B948" s="7"/>
+      <c r="I948" s="7"/>
+    </row>
+    <row r="949" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B949" s="7"/>
+      <c r="I949" s="7"/>
+    </row>
+    <row r="950" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B950" s="7"/>
+      <c r="I950" s="7"/>
+    </row>
+    <row r="951" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B951" s="7"/>
+      <c r="I951" s="7"/>
+    </row>
+    <row r="952" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B952" s="7"/>
+      <c r="I952" s="7"/>
+    </row>
+    <row r="953" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B953" s="7"/>
+      <c r="I953" s="7"/>
+    </row>
+    <row r="954" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B954" s="7"/>
+      <c r="I954" s="7"/>
+    </row>
+    <row r="955" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B955" s="7"/>
+      <c r="I955" s="7"/>
+    </row>
+    <row r="956" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B956" s="7"/>
+      <c r="I956" s="7"/>
+    </row>
+    <row r="957" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B957" s="7"/>
+      <c r="I957" s="7"/>
+    </row>
+    <row r="958" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B958" s="7"/>
+      <c r="I958" s="7"/>
+    </row>
+    <row r="959" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B959" s="7"/>
+      <c r="I959" s="7"/>
+    </row>
+    <row r="960" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B960" s="7"/>
+      <c r="I960" s="7"/>
+    </row>
+    <row r="961" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B961" s="7"/>
+      <c r="I961" s="7"/>
+    </row>
+    <row r="962" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B962" s="7"/>
+      <c r="I962" s="7"/>
+    </row>
+    <row r="963" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B963" s="7"/>
+      <c r="I963" s="7"/>
+    </row>
+    <row r="964" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B964" s="7"/>
+      <c r="I964" s="7"/>
+    </row>
+    <row r="965" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B965" s="7"/>
+      <c r="I965" s="7"/>
+    </row>
+    <row r="966" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B966" s="7"/>
+      <c r="I966" s="7"/>
+    </row>
+    <row r="967" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B967" s="7"/>
+      <c r="I967" s="7"/>
+    </row>
+    <row r="968" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B968" s="7"/>
+      <c r="I968" s="7"/>
+    </row>
+    <row r="969" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B969" s="7"/>
+      <c r="I969" s="7"/>
+    </row>
+    <row r="970" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B970" s="7"/>
+      <c r="I970" s="7"/>
+    </row>
+    <row r="971" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B971" s="7"/>
+      <c r="I971" s="7"/>
+    </row>
+    <row r="972" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B972" s="7"/>
+      <c r="I972" s="7"/>
+    </row>
+    <row r="973" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B973" s="7"/>
+      <c r="I973" s="7"/>
+    </row>
+    <row r="974" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B974" s="7"/>
+      <c r="I974" s="7"/>
+    </row>
+    <row r="975" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B975" s="7"/>
+      <c r="I975" s="7"/>
+    </row>
+    <row r="976" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B976" s="7"/>
+      <c r="I976" s="7"/>
+    </row>
+    <row r="977" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B977" s="7"/>
+      <c r="I977" s="7"/>
+    </row>
+    <row r="978" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B978" s="7"/>
+      <c r="I978" s="7"/>
+    </row>
+    <row r="979" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B979" s="7"/>
+      <c r="I979" s="7"/>
+    </row>
+    <row r="980" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B980" s="7"/>
+      <c r="I980" s="7"/>
+    </row>
+    <row r="981" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B981" s="7"/>
+      <c r="I981" s="7"/>
+    </row>
+    <row r="982" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B982" s="7"/>
+      <c r="I982" s="7"/>
+    </row>
+    <row r="983" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B983" s="7"/>
+      <c r="I983" s="7"/>
+    </row>
+    <row r="984" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B984" s="7"/>
+      <c r="I984" s="7"/>
+    </row>
+    <row r="985" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B985" s="7"/>
+      <c r="I985" s="7"/>
+    </row>
+    <row r="986" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B986" s="7"/>
+      <c r="I986" s="7"/>
+    </row>
+    <row r="987" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B987" s="7"/>
+      <c r="I987" s="7"/>
+    </row>
+    <row r="988" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B988" s="7"/>
+      <c r="I988" s="7"/>
+    </row>
+    <row r="989" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B989" s="7"/>
+      <c r="I989" s="7"/>
+    </row>
+    <row r="990" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B990" s="7"/>
+      <c r="I990" s="7"/>
+    </row>
+    <row r="991" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B991" s="7"/>
+      <c r="I991" s="7"/>
+    </row>
+    <row r="992" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B992" s="7"/>
+      <c r="I992" s="7"/>
+    </row>
+    <row r="993" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B993" s="7"/>
+      <c r="I993" s="7"/>
+    </row>
+    <row r="994" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B994" s="7"/>
+      <c r="I994" s="7"/>
+    </row>
+    <row r="995" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B995" s="7"/>
+      <c r="I995" s="7"/>
+    </row>
+    <row r="996" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B996" s="7"/>
+      <c r="I996" s="7"/>
+    </row>
+    <row r="997" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B997" s="7"/>
+      <c r="I997" s="7"/>
+    </row>
+    <row r="998" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B998" s="7"/>
+      <c r="I998" s="7"/>
+    </row>
+    <row r="999" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B999" s="7"/>
+      <c r="I999" s="7"/>
+    </row>
+    <row r="1000" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1000" s="7"/>
+      <c r="I1000" s="7"/>
+    </row>
+    <row r="1001" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1001" s="7"/>
+      <c r="I1001" s="7"/>
+    </row>
+    <row r="1002" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1002" s="7"/>
+      <c r="I1002" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D4:I4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>